--- a/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication freshwater results.xlsx
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-6.827517138363052e-07</v>
+        <v>-6.827517138363051e-07</v>
       </c>
       <c r="C9" t="n">
         <v>-8.378385746305962e-07</v>
@@ -2775,7 +2775,7 @@
         <v>4.328916566978704e-07</v>
       </c>
       <c r="E10" t="n">
-        <v>4.825636639710634e-08</v>
+        <v>4.825636639710655e-08</v>
       </c>
       <c r="F10" t="n">
         <v>-1.769329369126187e-07</v>
@@ -3033,10 +3033,10 @@
         <v>6.063548085429165e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="E13" t="n">
         <v>6.229548276206913e-06</v>
@@ -3048,19 +3048,19 @@
         <v>6.492229938698328e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="J13" t="n">
         <v>5.993430600708656e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="M13" t="n">
         <v>6.418606304073e-06</v>
@@ -3078,13 +3078,13 @@
         <v>5.993771041657327e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="U13" t="n">
         <v>6.245547282680204e-06</v>
@@ -3105,7 +3105,7 @@
         <v>6.056952696731232e-06</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.418606304073045e-06</v>
+        <v>6.418606304073046e-06</v>
       </c>
       <c r="AB13" t="n">
         <v>6.789494302934729e-06</v>
@@ -3212,10 +3212,10 @@
         <v>-1.116711400260627e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.406830561273074e-07</v>
+        <v>-4.406830561273076e-07</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.63792352532263e-07</v>
+        <v>-9.637923525322634e-07</v>
       </c>
       <c r="F15" t="n">
         <v>-1.67372051387918e-07</v>
@@ -3278,7 +3278,7 @@
         <v>1.181158066619512e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>-7.036090307930336e-07</v>
+        <v>-7.036090307930338e-07</v>
       </c>
       <c r="AA15" t="n">
         <v>1.077027175028201e-06</v>
@@ -3303,7 +3303,7 @@
         <v>-4.921151722419515e-07</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.811732001079962e-07</v>
+        <v>-6.811732001079964e-07</v>
       </c>
       <c r="F16" t="n">
         <v>-7.918594700729161e-07</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.782240757138678e-05</v>
+        <v>9.782240757138674e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.205460766543282e-06</v>
+        <v>2.205460766543284e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.982291383554144e-05</v>
+        <v>2.982291383554119e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.550142432573825e-05</v>
+        <v>2.550142432573821e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.967426048859653e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.078709788081647e-05</v>
+        <v>2.07870978808164e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.65625150063651e-06</v>
+        <v>1.656251500636486e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.376378651028569e-05</v>
+        <v>3.376378651028541e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.985616050410944e-05</v>
+        <v>3.985616050410919e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.377742219642079e-05</v>
+        <v>5.377742219642051e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000190433851266018</v>
+        <v>0.0001904338512660173</v>
       </c>
       <c r="M2" t="n">
-        <v>6.654836658756749e-05</v>
+        <v>6.65483665875674e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.090517871853253e-05</v>
+        <v>1.090517871853242e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.857667423913628e-05</v>
+        <v>1.857667423913648e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>6.403071868932761e-05</v>
+        <v>6.403071868932769e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.495357658384492e-05</v>
+        <v>2.495357658384491e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>3.499237875897919e-06</v>
+        <v>3.499237875897876e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>6.157683204438633e-05</v>
+        <v>6.157683204438622e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.865975613314803e-05</v>
+        <v>2.865975613314791e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001306434298153737</v>
+        <v>0.0001306434298153739</v>
       </c>
       <c r="V2" t="n">
-        <v>3.01725294588985e-05</v>
+        <v>3.017252945889852e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.592196947327573e-05</v>
+        <v>2.592196947327565e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0001034501001457701</v>
+        <v>0.0001034501001457699</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.022642896204924e-05</v>
+        <v>4.022642896204938e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.414007901047022e-05</v>
+        <v>5.414007901047017e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.121668318650604e-05</v>
+        <v>4.121668318650582e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.808212897536435e-05</v>
+        <v>8.808212897536423e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.309695110196079e-06</v>
+        <v>2.309695110195544e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>3.065049193328113e-06</v>
+        <v>3.065049193328115e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.581484362408248e-06</v>
+        <v>2.581484362408253e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>2.332819194144165e-06</v>
+        <v>2.332819194144167e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.388051027174152e-06</v>
+        <v>3.388051027173998e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.142899266483827e-06</v>
+        <v>3.142899266483711e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.206793625909325e-06</v>
+        <v>3.206793625909326e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.510505453620353e-06</v>
+        <v>2.510505453619833e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.700767642315401e-06</v>
+        <v>2.700767642315264e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65412978249085e-06</v>
+        <v>2.654129782490791e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.134169863580747e-06</v>
+        <v>2.134169863580209e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.767170300360887e-06</v>
+        <v>2.767170300360515e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.812231603981673e-06</v>
+        <v>2.812231603981649e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.203025151406024e-06</v>
+        <v>3.203025151405837e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.216029249190957e-06</v>
+        <v>2.216029249190714e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.091333286915988e-06</v>
+        <v>4.091333286916357e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.293104306616496e-06</v>
+        <v>2.293104306616326e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.202849621001378e-06</v>
+        <v>3.202849621001877e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.257207372007751e-06</v>
+        <v>4.257207372007748e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.670680213029542e-05</v>
+        <v>4.6706802130295e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176797402088606e-05</v>
+        <v>1.176797402088602e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192178515394942e-05</v>
+        <v>2.192178515394909e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.025400373200221e-05</v>
+        <v>2.025400373200217e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.814898877520539e-05</v>
+        <v>1.81489887752051e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.862833634235999e-05</v>
+        <v>1.862833634235976e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.165536748252446e-05</v>
+        <v>1.16553674825242e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.33581869678303e-05</v>
+        <v>2.335818696783015e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.502413586444096e-05</v>
+        <v>2.50241358644408e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.065292216345103e-05</v>
+        <v>3.065292216345086e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.046258585851132e-05</v>
+        <v>8.046258585851046e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.531028789145563e-05</v>
+        <v>3.531028789145531e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.50264928470609e-05</v>
+        <v>1.502649284706074e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.78226628810724e-05</v>
+        <v>1.78226628810721e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.439012833482942e-05</v>
+        <v>3.439012833482884e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.014696890435091e-05</v>
+        <v>2.014696890435042e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23271143748686e-05</v>
+        <v>1.232711437486835e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.349571546774014e-05</v>
+        <v>3.349571546773972e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.149782782991433e-05</v>
+        <v>2.149782782991389e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.866967933432741e-05</v>
+        <v>5.866967933432712e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.850963474082705e-05</v>
+        <v>1.850963474082719e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.049993674110488e-05</v>
+        <v>2.049993674110466e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.875802998995551e-05</v>
+        <v>4.875802998995537e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.5713744253319e-05</v>
+        <v>2.571374425331866e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.078510631364078e-05</v>
+        <v>3.078510631364026e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.607468028998134e-05</v>
+        <v>2.607468028998116e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.323372539451081e-05</v>
+        <v>4.323372539451044e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.189354000508659e-05</v>
+        <v>1.189354000508657e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.208128390865221e-05</v>
+        <v>1.208128390865201e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.189995475489169e-05</v>
+        <v>1.189995475489166e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.182823705686234e-05</v>
+        <v>1.1828237056862e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.228658807413067e-05</v>
+        <v>1.228658807413098e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.16425832522054e-05</v>
+        <v>1.164258325220564e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.222302834123352e-05</v>
+        <v>1.222302834123326e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.196673301723087e-05</v>
+        <v>1.196673301723033e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.203608135083876e-05</v>
+        <v>1.203608135083868e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.201908239858217e-05</v>
+        <v>1.201908239858176e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.182956311381678e-05</v>
+        <v>1.18295631138162e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.20602843399568e-05</v>
+        <v>1.206028433995683e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>8.537127453548146e-06</v>
+        <v>8.537127453548393e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.221914831509682e-05</v>
+        <v>1.221914831509665e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.185939989863053e-05</v>
+        <v>1.185939989863026e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.254292619944927e-05</v>
+        <v>1.254292619944888e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.188749285200116e-05</v>
+        <v>1.188749285200075e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.221908433632547e-05</v>
+        <v>1.221908433632544e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.268052579201287e-05</v>
+        <v>1.268052579201281e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.625925927483705e-05</v>
+        <v>3.625925927483717e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.320431165427563e-06</v>
+        <v>1.320431165427564e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.147424229849098e-05</v>
+        <v>1.147424229849106e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.806460876543823e-06</v>
+        <v>9.80646087654383e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.701445919746891e-06</v>
+        <v>7.701445919746892e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.151163605768404e-06</v>
+        <v>8.151163605768112e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.207824627066096e-06</v>
+        <v>1.207824627066241e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.291064411237194e-05</v>
+        <v>1.291064411237206e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.506539950759862e-05</v>
+        <v>1.50653995075986e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.02053793079927e-05</v>
+        <v>2.020537930799301e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>7.001504300305286e-05</v>
+        <v>7.001504300305281e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.48627450359971e-05</v>
+        <v>2.486274503599703e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.578949991602484e-06</v>
+        <v>4.578949991602806e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>7.345490144480748e-06</v>
+        <v>7.345490144480463e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>2.391295559823769e-05</v>
+        <v>2.391295559823782e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.699426048892416e-06</v>
+        <v>9.69942604889248e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.879571519410227e-06</v>
+        <v>1.879571519410277e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>2.304817261228181e-05</v>
+        <v>2.304817261228188e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.105028497445587e-05</v>
+        <v>1.105028497445613e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.819250659773561e-05</v>
+        <v>4.819250659773548e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.148233767400548e-05</v>
+        <v>1.148233767400553e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.002276400451323e-05</v>
+        <v>1.002276400451318e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>3.828085725336386e-05</v>
+        <v>3.828085725336358e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.526620139786066e-05</v>
+        <v>1.526620139786072e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.03375634581824e-05</v>
+        <v>2.033756345818246e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.562713743452295e-05</v>
+        <v>1.56271374345231e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.278618253905219e-05</v>
+        <v>3.27861825390522e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.445997149628295e-06</v>
+        <v>1.445997149628269e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.633741053193709e-06</v>
+        <v>1.633741053193712e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.452411899433374e-06</v>
+        <v>1.452411899433373e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.380694201403697e-06</v>
+        <v>1.380694201403698e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.809415337538935e-06</v>
+        <v>1.809415337539459e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6838468953634e-06</v>
+        <v>1.683846895362892e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.77548548577497e-06</v>
+        <v>1.775485485774969e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.519190161772383e-06</v>
+        <v>1.51919016177141e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.558908614247021e-06</v>
+        <v>1.558908614247016e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.541909661990423e-06</v>
+        <v>1.541909661990309e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.382020258358361e-06</v>
+        <v>1.382020258358608e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.583111603365102e-06</v>
+        <v>1.583111603365356e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.50983038672649e-06</v>
+        <v>1.509830386726507e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.741975578505003e-06</v>
+        <v>1.741975578505343e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.382227162038791e-06</v>
+        <v>1.382227162038927e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.095383343990811e-06</v>
+        <v>2.095383343991274e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.43994999654262e-06</v>
+        <v>1.439949996541977e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.771541480866985e-06</v>
+        <v>1.771541480866918e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.232982936554495e-06</v>
+        <v>2.232982936554496e-06</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="P8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="R8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>4.636890134413883e-06</v>
+        <v>4.636890134413886e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="U8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="X8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.241587692452077e-06</v>
+        <v>3.24158769245208e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5633,10 +5633,10 @@
         <v>0.0001032310387282072</v>
       </c>
       <c r="C9" t="n">
-        <v>6.193146486924661e-07</v>
+        <v>6.193146486924763e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>3.015177950226119e-05</v>
+        <v>3.015177950226124e-05</v>
       </c>
       <c r="E9" t="n">
         <v>2.566413934542901e-05</v>
@@ -5645,70 +5645,70 @@
         <v>1.936967732016603e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.044096108001759e-05</v>
+        <v>2.044096108001764e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1901672305155e-07</v>
+        <v>-1.19016723051532e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>3.438704714841239e-05</v>
+        <v>3.438704714841235e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.099896852007884e-05</v>
+        <v>4.099896852007878e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.589576125799576e-05</v>
+        <v>5.589576125799577e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002027608341608073</v>
+        <v>0.000202760834160807</v>
       </c>
       <c r="M9" t="n">
-        <v>6.961649474445522e-05</v>
+        <v>6.961649474445519e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>9.820833010891886e-06</v>
+        <v>9.820833010891881e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>1.806541218347704e-05</v>
+        <v>1.806541218347706e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>6.691500965470304e-05</v>
+        <v>6.691500965470307e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.491868819929312e-05</v>
+        <v>2.491868819929314e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.861646244687833e-06</v>
+        <v>1.861646244687841e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>6.427781034064095e-05</v>
+        <v>6.42778103406409e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89017304418363e-05</v>
+        <v>2.890173044183626e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001385038894636309</v>
+        <v>0.0001385038894636311</v>
       </c>
       <c r="V9" t="n">
-        <v>3.068526747555029e-05</v>
+        <v>3.068526747555037e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.595942293291032e-05</v>
+        <v>2.595942293291027e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001092791367638325</v>
+        <v>0.0001092791367638324</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.133246831363015e-05</v>
+        <v>4.133246831363017e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.628550962034289e-05</v>
+        <v>5.628550962034281e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.239669748936172e-05</v>
+        <v>4.239669748936162e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.263268133250065e-05</v>
+        <v>9.26326813325005e-05</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.832410778380523e-07</v>
+        <v>5.832410778380555e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>1.032011339741185e-06</v>
+        <v>1.032011339741188e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>7.327785127743835e-07</v>
+        <v>7.327785127743905e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>1.742153405933057e-06</v>
+        <v>1.742153405933061e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>1.543116900995308e-06</v>
+        <v>1.543116900995311e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>7.990525543083218e-07</v>
+        <v>7.990525543083223e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>1.003527897353615e-06</v>
+        <v>1.003527897353616e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>9.534060499602098e-07</v>
+        <v>9.534060499602148e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.94603570507028e-07</v>
+        <v>3.946035705070291e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.074891032488749e-06</v>
+        <v>1.074891032488754e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.281073567786573e-06</v>
+        <v>1.281073567786575e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.543305544045902e-06</v>
+        <v>1.543305544045905e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>4.825780969693598e-07</v>
+        <v>4.825780969693627e-07</v>
       </c>
       <c r="Y10" t="n">
         <v>2.497972953183333e-06</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.654108916272344e-07</v>
+        <v>5.654108916272367e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.543116900995376e-06</v>
+        <v>1.543116900995381e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.545787461743737e-06</v>
+        <v>2.545787461743741e-06</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>9.686603601236057e-06</v>
+        <v>9.686603601235702e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.081659829109239e-05</v>
+        <v>1.081659829109225e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>7.167397182735285e-06</v>
+        <v>7.167397182735048e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.013077165322027e-05</v>
+        <v>1.013077165321991e-05</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.927812993500176e-05</v>
+        <v>5.927812993500173e-05</v>
       </c>
       <c r="C12" t="n">
-        <v>8.841857758211121e-06</v>
+        <v>8.841857758210923e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>2.335781535241228e-05</v>
+        <v>2.335781535241199e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>2.115202607821498e-05</v>
+        <v>2.115202607821468e-05</v>
       </c>
       <c r="F12" t="n">
         <v>1.805813790159053e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>1.858470111622472e-05</v>
+        <v>1.858470111622461e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>8.478949110529811e-06</v>
+        <v>8.478949110529501e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>2.54395571188531e-05</v>
+        <v>2.54395571188528e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.824531658640341e-05</v>
+        <v>2.824531658640306e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.601163714903655e-05</v>
+        <v>3.601163714903642e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001081995557971084</v>
+        <v>0.000108199555797108</v>
       </c>
       <c r="M12" t="n">
-        <v>4.275572662610273e-05</v>
+        <v>4.275572662610233e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.336463806152226e-05</v>
+        <v>1.336463806152206e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.741705841467194e-05</v>
+        <v>1.741705841467179e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>4.142787799583606e-05</v>
+        <v>4.142787799583588e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.078561788033797e-05</v>
+        <v>2.078561788033783e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>9.452495334682346e-06</v>
+        <v>9.452495334682166e-06</v>
       </c>
       <c r="S12" t="n">
-        <v>4.013162745934365e-05</v>
+        <v>4.013162745934352e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>2.274338444589053e-05</v>
+        <v>2.274338444589033e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>7.661563318915777e-05</v>
+        <v>7.661563318915781e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>2.065666378935064e-05</v>
+        <v>2.065666378935073e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>2.129716547160436e-05</v>
+        <v>2.129716547160418e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>6.225092394478113e-05</v>
+        <v>6.225092394478094e-05</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.885340826903855e-05</v>
+        <v>2.885340826903843e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.620320838185745e-05</v>
+        <v>3.62032083818574e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.937650397615374e-05</v>
+        <v>2.937650397615355e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.406876771999266e-05</v>
+        <v>5.406876771999235e-05</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.824126680653268e-06</v>
+        <v>8.824126680652863e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>9.044708678248998e-06</v>
+        <v>9.044708678248788e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>8.897628133208731e-06</v>
+        <v>8.897628133208681e-06</v>
       </c>
       <c r="G13" t="n">
-        <v>9.393761565294125e-06</v>
+        <v>9.393761565294041e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>8.851762008906202e-06</v>
+        <v>8.851762008906053e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>9.295930060890467e-06</v>
+        <v>9.295930060890065e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>8.930203510214056e-06</v>
+        <v>8.930203510213916e-06</v>
       </c>
       <c r="O13" t="n">
-        <v>9.030708341877292e-06</v>
+        <v>9.030708341877165e-06</v>
       </c>
       <c r="P13" t="n">
-        <v>9.006072179101317e-06</v>
+        <v>9.006072179101049e-06</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.731406548057743e-06</v>
+        <v>8.731406548057716e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>9.065785137821782e-06</v>
+        <v>9.065785137821791e-06</v>
       </c>
       <c r="V13" t="n">
-        <v>6.203754627412365e-06</v>
+        <v>6.203754627412268e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>9.296022783747715e-06</v>
+        <v>9.296022783747417e-06</v>
       </c>
       <c r="X13" t="n">
-        <v>8.774648265328282e-06</v>
+        <v>8.774648265327955e-06</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.765266096025015e-06</v>
+        <v>9.765266096025022e-06</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.815362690643667e-06</v>
+        <v>8.815362690643463e-06</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.295930060890494e-06</v>
+        <v>9.29593006089008e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.788768143080452e-06</v>
+        <v>9.788768143080334e-06</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>1.121737913314769e-06</v>
+        <v>1.121737913314775e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>1.123359332193682e-06</v>
+        <v>1.123359332193689e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>1.121737913314769e-06</v>
+        <v>1.121737913314775e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>1.121737913314769e-06</v>
+        <v>1.121737913314775e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="S14" t="n">
         <v>1.833042474053241e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.12173791331477e-06</v>
+        <v>1.121737913314775e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.124816997518881e-06</v>
+        <v>1.124816997518882e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.121737913314769e-06</v>
+        <v>1.121737913314775e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.121737913314769e-06</v>
+        <v>1.121737913314775e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.147215836181009e-06</v>
+        <v>1.147215836181014e-06</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.029457411796259e-05</v>
+        <v>5.029457411796264e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.416980588280382e-07</v>
+        <v>-1.416980588280312e-07</v>
       </c>
       <c r="D15" t="n">
-        <v>1.437425953537306e-05</v>
+        <v>1.437425953537305e-05</v>
       </c>
       <c r="E15" t="n">
         <v>1.216847026117577e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.074582084551532e-06</v>
+        <v>9.074582084551534e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>9.575667376319391e-06</v>
+        <v>9.575667376319329e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.046067065093505e-07</v>
+        <v>-5.046067065093402e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>1.645600130181393e-05</v>
+        <v>1.645600130181394e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>1.968207231736128e-05</v>
+        <v>1.968207231736119e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>2.702808133199737e-05</v>
+        <v>2.702808133199735e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>9.921599998006921e-05</v>
+        <v>9.921599998006885e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.377217080906357e-05</v>
+        <v>3.377217080906352e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.381082244483104e-06</v>
+        <v>4.381082244483109e-06</v>
       </c>
       <c r="O15" t="n">
-        <v>8.408024674766545e-06</v>
+        <v>8.408024674766572e-06</v>
       </c>
       <c r="P15" t="n">
-        <v>3.241884425593061e-05</v>
+        <v>3.241884425593063e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.180206206329894e-05</v>
+        <v>1.180206206329892e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>4.689395176431906e-07</v>
+        <v>4.689395176431921e-07</v>
       </c>
       <c r="S15" t="n">
-        <v>3.11480716423045e-05</v>
+        <v>3.114807164230445e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.375982862885132e-05</v>
+        <v>1.375982862885131e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>6.760659944925245e-05</v>
+        <v>6.760659944925254e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>1.461408360413429e-05</v>
+        <v>1.461408360413428e-05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.228813173169896e-05</v>
+        <v>1.228813173169895e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>5.324189020487575e-05</v>
+        <v>5.324189020487576e-05</v>
       </c>
       <c r="Y15" t="n">
         <v>1.986985245199942e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.721965256481829e-05</v>
+        <v>2.721965256481826e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03929481591146e-05</v>
+        <v>2.039294815911457e-05</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.508521190295354e-05</v>
+        <v>4.50852119029535e-05</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.594291363859208e-07</v>
+        <v>-1.594291363859164e-07</v>
       </c>
       <c r="C16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="D16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="E16" t="n">
-        <v>6.115286120976002e-08</v>
+        <v>6.11528612097596e-08</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.592768383042733e-08</v>
+        <v>-8.592768383042352e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>3.847278253887243e-07</v>
+        <v>3.847278253887304e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>2.885177398639714e-07</v>
+        <v>2.885177398639742e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.123742438512597e-07</v>
+        <v>3.123742438512647e-07</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.335230682505222e-08</v>
+        <v>-5.335230682504777e-08</v>
       </c>
       <c r="O16" t="n">
-        <v>2.167460197182824e-08</v>
+        <v>2.16746019718312e-08</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.96156080405377e-09</v>
+        <v>-2.961560804048264e-09</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.521492689813536e-07</v>
       </c>
       <c r="R16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="S16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="U16" t="n">
-        <v>5.675139791647018e-08</v>
+        <v>5.675139791647399e-08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.611744421959775e-07</v>
+        <v>1.611744421959783e-07</v>
       </c>
       <c r="W16" t="n">
-        <v>2.869890438422711e-07</v>
+        <v>2.86989043842273e-07</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.343854745771641e-07</v>
+        <v>-2.343854745771603e-07</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.81710278985931e-07</v>
+        <v>7.817102789859329e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1.68193126395432e-07</v>
+        <v>-1.681931263954269e-07</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.123742438512955e-07</v>
+        <v>3.12374243851301e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.052123260413233e-07</v>
+        <v>8.052123260413259e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.361228054036244e-05</v>
+        <v>8.361228054036252e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>3.630805887471077e-06</v>
+        <v>3.630805887471076e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.692907987035417e-05</v>
+        <v>2.692907987035408e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.893727453811066e-05</v>
+        <v>1.893727453811072e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.276392136224743e-05</v>
+        <v>2.276392136224741e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.035382995532182e-05</v>
+        <v>2.03538299553216e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.865927591754917e-06</v>
+        <v>1.865927591754914e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.758014447910343e-05</v>
+        <v>3.758014447910344e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.067210646263492e-05</v>
+        <v>4.067210646263484e-05</v>
       </c>
       <c r="K2" t="n">
         <v>6.263246438122043e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001567181171912086</v>
+        <v>0.0001567181171912084</v>
       </c>
       <c r="M2" t="n">
-        <v>5.95860588531257e-05</v>
+        <v>5.95860588531256e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.620312852358134e-06</v>
+        <v>9.620312852358075e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.311500709392581e-05</v>
+        <v>1.311500709392573e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>5.916820260331482e-05</v>
+        <v>5.91682026033148e-05</v>
       </c>
       <c r="Q2" t="n">
         <v>3.239157109912483e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>9.057806884477527e-06</v>
+        <v>9.057806884477468e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>5.793091209096902e-05</v>
+        <v>5.793091209096905e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.945054252321878e-05</v>
+        <v>2.945054252321873e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001469572122683625</v>
+        <v>0.0001469572122683623</v>
       </c>
       <c r="V2" t="n">
-        <v>5.438149093719454e-05</v>
+        <v>5.438149093719458e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.092811981226663e-05</v>
+        <v>3.092811981226661e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0001169345115766678</v>
+        <v>0.0001169345115766679</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.466077729164929e-05</v>
+        <v>6.466077729164913e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.284898100546345e-05</v>
+        <v>5.284898100546346e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.401507269032608e-05</v>
+        <v>4.4015072690326e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.369526064661364e-05</v>
+        <v>8.369526064661355e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.409067581554261e-06</v>
+        <v>2.409067581554093e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>3.193463030214426e-06</v>
+        <v>3.193463030214422e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.682406421790033e-06</v>
+        <v>2.682406421790027e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>2.45041466192636e-06</v>
+        <v>2.450414661926357e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.512681335981746e-06</v>
+        <v>3.512681335981843e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.281502837917866e-06</v>
+        <v>3.281502837917886e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.311688291962699e-06</v>
+        <v>3.311688291962695e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.614581413801968e-06</v>
+        <v>2.614581413801844e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.80930002670999e-06</v>
+        <v>2.809300026709941e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.761569789630583e-06</v>
+        <v>2.761569789630619e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.229431087374026e-06</v>
+        <v>2.229431087374029e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.879025867690364e-06</v>
+        <v>2.879025867690404e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.976199155484471e-06</v>
+        <v>2.976199155484418e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.323321683715786e-06</v>
+        <v>3.323321683715771e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.313207827913472e-06</v>
+        <v>2.313207827913416e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.235460555116645e-06</v>
+        <v>4.235460555116707e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.392088179173327e-06</v>
+        <v>2.392088179173402e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.323142041977853e-06</v>
+        <v>3.323142041977808e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.388212433811788e-06</v>
+        <v>4.388212433811782e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.155053220233175e-05</v>
+        <v>4.155053220233206e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.231581134650239e-05</v>
+        <v>1.231581134650255e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.089017116586109e-05</v>
+        <v>2.089017116586104e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.787937176144022e-05</v>
+        <v>1.787937176144044e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.930779813641303e-05</v>
+        <v>1.930779813641314e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.849356978231446e-05</v>
+        <v>1.849356978231437e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.175494646670462e-05</v>
+        <v>1.175494646670472e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4772359144635e-05</v>
+        <v>2.477235914463505e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.562629863282341e-05</v>
+        <v>2.56262986328235e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.39036355697638e-05</v>
+        <v>3.390363556976388e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>6.819675120948986e-05</v>
+        <v>6.819675120948983e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.278597753484194e-05</v>
+        <v>3.278597753484202e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.458132883760551e-05</v>
+        <v>1.458132883760546e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.585510385188528e-05</v>
+        <v>1.585510385188522e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.264095283113288e-05</v>
+        <v>3.264095283113283e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.288118507493748e-05</v>
+        <v>2.288118507493747e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.437630201759159e-05</v>
+        <v>1.437630201759164e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.218997496838153e-05</v>
+        <v>3.218997496838149e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18092146943209e-05</v>
+        <v>2.180921469432087e-05</v>
       </c>
       <c r="U4" t="n">
         <v>6.463901598344482e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.918798005375088e-05</v>
+        <v>2.918798005375083e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.234777426559032e-05</v>
+        <v>2.234777426559062e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>5.36960941256728e-05</v>
+        <v>5.369609412567279e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.464293180796254e-05</v>
+        <v>3.464293180796244e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.033767076276247e-05</v>
+        <v>3.033767076276242e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.711781491488358e-05</v>
+        <v>2.711781491488381e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.165083831484682e-05</v>
+        <v>4.165083831484679e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.195291461511472e-05</v>
+        <v>1.195291461511481e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.215640501057148e-05</v>
+        <v>1.215640501057161e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.195466320733962e-05</v>
+        <v>1.195466320733979e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190376347738471e-05</v>
+        <v>1.190376347738488e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.235516886931653e-05</v>
+        <v>1.235516886931666e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.199786267424909e-05</v>
+        <v>1.19978626742492e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.227463027231984e-05</v>
+        <v>1.227463027231999e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.202782199370374e-05</v>
+        <v>1.202782199370371e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.209879464160734e-05</v>
+        <v>1.209879464160733e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.208139753066861e-05</v>
+        <v>1.208139753066859e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.188743922238422e-05</v>
+        <v>1.188743922238442e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21242088918825e-05</v>
+        <v>1.212420889188264e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04513548307296e-05</v>
+        <v>1.045135483072968e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22861494996389e-05</v>
+        <v>1.228614949963915e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.19179748605547e-05</v>
+        <v>1.191797486055465e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26186134073891e-05</v>
+        <v>1.261861340738924e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.194672582232908e-05</v>
+        <v>1.194672582232893e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.228608402233488e-05</v>
+        <v>1.228608402233503e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27443505116585e-05</v>
+        <v>1.274435051165846e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.112365918053894e-05</v>
+        <v>3.112365918053892e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.888938324709598e-06</v>
+        <v>1.888938324709597e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.046329814406831e-05</v>
+        <v>1.04632981440682e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>7.452498739647426e-06</v>
+        <v>7.452498739647444e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>8.880925114620249e-06</v>
+        <v>8.880925114620232e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.035470897592462e-06</v>
+        <v>8.03547089759234e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.328073444911823e-06</v>
+        <v>1.328073444911811e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.43454861228422e-05</v>
+        <v>1.434548612284212e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.541678023997534e-05</v>
+        <v>1.541678023997538e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.347676254797105e-05</v>
+        <v>2.347676254797112e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.776987818769706e-05</v>
+        <v>5.776987818769689e-05</v>
       </c>
       <c r="M6" t="n">
         <v>2.235910451304909e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.154455815812718e-06</v>
+        <v>4.154455815812632e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>5.39700496716329e-06</v>
+        <v>5.397004967163199e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21828539464109e-05</v>
+        <v>2.218285394641078e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.245431205314471e-05</v>
+        <v>1.245431205314463e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.949428995798791e-06</v>
+        <v>3.949428995798718e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>2.176310194658878e-05</v>
+        <v>2.176310194658873e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.138234167252812e-05</v>
+        <v>1.138234167252804e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.418091709872292e-05</v>
+        <v>5.418091709872284e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.037881533487503e-05</v>
+        <v>2.037881533487501e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.188967538086832e-05</v>
+        <v>1.18896753808685e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.323799524095087e-05</v>
+        <v>4.323799524095083e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.421605878616974e-05</v>
+        <v>2.421605878616956e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.991079774096967e-05</v>
+        <v>1.991079774096959e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.669094189309077e-05</v>
+        <v>1.66909418930908e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.12239652930541e-05</v>
+        <v>3.122396529305401e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.52604159332192e-06</v>
+        <v>1.526041593321981e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.72953198877866e-06</v>
+        <v>1.729531988778658e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.527790185546811e-06</v>
+        <v>1.527790185546809e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.476890455591917e-06</v>
+        <v>1.476890455591915e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.897069984594541e-06</v>
+        <v>1.897069984594525e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.788344281401069e-06</v>
+        <v>1.788344281401105e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.847757250527055e-06</v>
+        <v>1.847757250527052e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.600948971910948e-06</v>
+        <v>1.600948971910768e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.640695756885323e-06</v>
+        <v>1.640695756885222e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.623298645946623e-06</v>
+        <v>1.623298645946536e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.460566200591437e-06</v>
+        <v>1.460566200591391e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.666110007160501e-06</v>
+        <v>1.666110007160451e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.642190111853837e-06</v>
+        <v>1.642190111853863e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.828050614916898e-06</v>
+        <v>1.828050614916983e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.459875975832701e-06</v>
+        <v>1.459875975832529e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.191740385596312e-06</v>
+        <v>2.191740385596282e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.519852800536278e-06</v>
+        <v>1.519852800536096e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.859211000542089e-06</v>
+        <v>1.859211000542155e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.317477489865703e-06</v>
+        <v>2.3174774898657e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180872e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="P8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="R8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>4.491487207338758e-06</v>
+        <v>4.491487207338767e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="U8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="X8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.460613842180874e-06</v>
+        <v>3.460613842180869e-06</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.799734313700217e-05</v>
+        <v>8.799734313700235e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.180379616888336e-06</v>
+        <v>2.180379616888326e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>2.707973790288802e-05</v>
+        <v>2.707973790288795e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.865644435172149e-05</v>
+        <v>1.865644435172154e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.271203375202339e-05</v>
+        <v>2.271203375202333e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.001329716021623e-05</v>
+        <v>2.001329716021606e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.44293214104912e-07</v>
+        <v>1.442932141049239e-07</v>
       </c>
       <c r="I9" t="n">
         <v>3.85264688829567e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.189415944824704e-05</v>
+        <v>4.189415944824699e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.545027198434704e-05</v>
+        <v>6.545027198434708e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001665644043608802</v>
+        <v>0.0001665644043608801</v>
       </c>
       <c r="M9" t="n">
-        <v>6.21886002344055e-05</v>
+        <v>6.218860023440544e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>8.477954238095092e-06</v>
+        <v>8.477954238095064e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>1.223371258810642e-05</v>
+        <v>1.223371258810638e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>6.172721949402179e-05</v>
+        <v>6.172721949402177e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.295029355845682e-05</v>
+        <v>3.295029355845688e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>7.8734273926074e-06</v>
+        <v>7.873427392607393e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>6.039749968109525e-05</v>
+        <v>6.03974996810952e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.978956135470731e-05</v>
+        <v>2.97895613547073e-05</v>
       </c>
       <c r="U9" t="n">
         <v>0.0001560743306566922</v>
       </c>
       <c r="V9" t="n">
-        <v>5.668970122354615e-05</v>
+        <v>5.668970122354623e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>3.137751808497601e-05</v>
+        <v>3.137751808497598e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001238088444600676</v>
+        <v>0.0001238088444600677</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.763010593352889e-05</v>
+        <v>6.763010593352866e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.493593314930974e-05</v>
+        <v>5.493593314930975e-05</v>
       </c>
       <c r="AA9" t="n">
         <v>4.544210547100377e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.796804342546918e-05</v>
+        <v>8.796804342546895e-05</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.280073850473386e-07</v>
+        <v>7.280073850473346e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>1.187288987554844e-06</v>
+        <v>1.187288987554838e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>8.810473669259982e-07</v>
+        <v>8.810473669259957e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>1.914064386566027e-06</v>
+        <v>1.91406438656602e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>1.710365940606487e-06</v>
+        <v>1.71036594060648e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>9.488737150187175e-07</v>
+        <v>9.488737150187131e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>1.158138390489686e-06</v>
+        <v>1.158138390489676e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>1.106842561994379e-06</v>
+        <v>1.106842561994368e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.349515076663349e-07</v>
+        <v>5.349515076663302e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.23307296026085e-06</v>
+        <v>1.233072960260842e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.444280451822174e-06</v>
+        <v>1.444280451822165e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.710559002119554e-06</v>
+        <v>1.710559002119545e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>6.24986621203656e-07</v>
+        <v>6.249866212036496e-07</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.690837374369053e-06</v>
+        <v>2.690837374369045e-06</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.097595705427485e-07</v>
+        <v>7.09759570542743e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.710365940606693e-06</v>
+        <v>1.710365940606683e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.736521595288308e-06</v>
+        <v>2.736521595288302e-06</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>1.006561603801519e-05</v>
+        <v>1.006561603801524e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.027764549667584e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.078434597453354e-05</v>
+        <v>1.078434597453368e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>8.863041118714497e-06</v>
+        <v>8.863041118714637e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.027764549667569e-05</v>
+        <v>1.02776454966758e-05</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.182959802351644e-05</v>
+        <v>5.182959802351651e-05</v>
       </c>
       <c r="C12" t="n">
-        <v>9.648377813902317e-06</v>
+        <v>9.64837781390244e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>2.188704569328572e-05</v>
+        <v>2.18870456932859e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>1.774678267770254e-05</v>
+        <v>1.77467826777027e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>1.974020801643311e-05</v>
+        <v>1.974020801643323e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>1.841371034281079e-05</v>
+        <v>1.841371034281085e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>8.647589561804836e-06</v>
+        <v>8.647589561805005e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>2.751340510225409e-05</v>
+        <v>2.751340510225413e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.895668120913083e-05</v>
+        <v>2.895668120913091e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>4.074713909744327e-05</v>
+        <v>4.074713909744345e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>9.044730686298002e-05</v>
+        <v>9.044730686298015e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.914394447609645e-05</v>
+        <v>3.914394447609656e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.27437959105976e-05</v>
+        <v>1.274379591059775e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.458984666230934e-05</v>
+        <v>1.458984666230946e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>3.891716410759696e-05</v>
+        <v>3.891716410759709e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.477257310771473e-05</v>
+        <v>2.477257310771491e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.244665559071011e-05</v>
+        <v>1.244665559071007e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>3.826357299990188e-05</v>
+        <v>3.826357299990205e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>2.321899284058341e-05</v>
+        <v>2.321899284058354e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>8.529116883640317e-05</v>
+        <v>8.529116883640331e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>3.50264913771702e-05</v>
+        <v>3.502649137716985e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>2.399951396106215e-05</v>
+        <v>2.399951396106208e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>6.943186174135446e-05</v>
+        <v>6.943186174135465e-05</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.18185829246218e-05</v>
+        <v>4.181858292462184e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.557907414190269e-05</v>
+        <v>3.557907414190286e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.091261637522935e-05</v>
+        <v>3.09126163752296e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.181519647009911e-05</v>
+        <v>5.181519647009916e-05</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.934499922810835e-06</v>
+        <v>8.934499922810894e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>9.160248511655434e-06</v>
+        <v>9.160248511655533e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>9.009722966271067e-06</v>
+        <v>9.009722966271096e-06</v>
       </c>
       <c r="G13" t="n">
-        <v>9.517477104827868e-06</v>
+        <v>9.517477104827985e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>9.205324679181333e-06</v>
+        <v>9.205324679181358e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>9.417354137841724e-06</v>
+        <v>9.417354137841861e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>9.043061341430921e-06</v>
+        <v>9.043061341430873e-06</v>
       </c>
       <c r="O13" t="n">
-        <v>9.145920251791533e-06</v>
+        <v>9.14592025179159e-06</v>
       </c>
       <c r="P13" t="n">
-        <v>9.120707047445414e-06</v>
+        <v>9.120707047445547e-06</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.839608048960504e-06</v>
+        <v>8.839608048960606e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>9.182752498694419e-06</v>
+        <v>9.182752498694502e-06</v>
       </c>
       <c r="V13" t="n">
-        <v>7.871961974615339e-06</v>
+        <v>7.871961974615303e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>9.417449032485653e-06</v>
+        <v>9.417449032485711e-06</v>
       </c>
       <c r="X13" t="n">
-        <v>8.883862597186584e-06</v>
+        <v>8.883862597186614e-06</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.899280784513173e-06</v>
+        <v>9.89928078451328e-06</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.925530657873109e-06</v>
+        <v>8.925530657873136e-06</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.417354137841822e-06</v>
+        <v>9.417354137841957e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.921735741011931e-06</v>
+        <v>9.921735741012113e-06</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>1.285012839329923e-06</v>
+        <v>1.285012839329917e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>1.286731163872957e-06</v>
+        <v>1.286731163872949e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209264e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>1.285012839329923e-06</v>
+        <v>1.285012839329917e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>1.285012839329923e-06</v>
+        <v>1.285012839329917e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>1.818563581067109e-06</v>
+        <v>1.81856358106711e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.285012839329922e-06</v>
+        <v>1.285012839329917e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.288281766371521e-06</v>
+        <v>1.288281766371518e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.285012839329923e-06</v>
+        <v>1.285012839329917e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.285012839329923e-06</v>
+        <v>1.285012839329917e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.31186310320927e-06</v>
+        <v>1.311863103209265e-06</v>
       </c>
     </row>
     <row r="15">
@@ -7634,49 +7634,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.286381563004998e-05</v>
+        <v>4.286381563005005e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>6.82595420435888e-07</v>
+        <v>6.825954204358858e-07</v>
       </c>
       <c r="D15" t="n">
-        <v>1.292126329981929e-05</v>
+        <v>1.292126329981926e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>8.781000284236118e-06</v>
+        <v>8.781000284236128e-06</v>
       </c>
       <c r="F15" t="n">
-        <v>1.077442562296666e-05</v>
+        <v>1.077442562296664e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>9.421077685464996e-06</v>
+        <v>9.421077685464923e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.181928316616055e-07</v>
+        <v>-3.181928316615979e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>1.854762270878762e-05</v>
+        <v>1.854762270878763e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>2.017779633498862e-05</v>
+        <v>2.017779633498861e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.178135670397686e-05</v>
+        <v>3.178135670397692e-05</v>
       </c>
       <c r="L15" t="n">
         <v>8.148152446951353e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.017816208263005e-05</v>
+        <v>3.017816208263e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.778013517131171e-06</v>
+        <v>3.778013517131155e-06</v>
       </c>
       <c r="O15" t="n">
-        <v>5.59721400496357e-06</v>
+        <v>5.597214004963547e-06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.992453145025111e-05</v>
+        <v>2.992453145025113e-05</v>
       </c>
       <c r="Q15" t="n">
         <v>1.580679071424833e-05</v>
@@ -7685,31 +7685,31 @@
         <v>3.480873197243677e-06</v>
       </c>
       <c r="S15" t="n">
-        <v>2.929779060643548e-05</v>
+        <v>2.929779060643549e-05</v>
       </c>
       <c r="T15" t="n">
         <v>1.425321044711697e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>7.629853617905739e-05</v>
+        <v>7.629853617905731e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>2.745173202482669e-05</v>
+        <v>2.74517320248267e-05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.500688130371638e-05</v>
+        <v>1.500688130371635e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>6.043922908400863e-05</v>
+        <v>6.043922908400872e-05</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.285280053115536e-05</v>
+        <v>3.285280053115525e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.661329174843629e-05</v>
+        <v>2.661329174843627e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.194683398176292e-05</v>
+        <v>2.194683398176293e-05</v>
       </c>
       <c r="AB15" t="n">
         <v>4.284941407663258e-05</v>
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.128247065559605e-08</v>
+        <v>-3.128247065560092e-08</v>
       </c>
       <c r="C16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="D16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="E16" t="n">
-        <v>1.944661181889931e-07</v>
+        <v>1.944661181889876e-07</v>
       </c>
       <c r="F16" t="n">
-        <v>4.394057280464204e-08</v>
+        <v>4.394057280463717e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>5.248444474820945e-07</v>
+        <v>5.24844447482092e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>4.264398050390882e-07</v>
+        <v>4.264398050390814e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="M16" t="n">
-        <v>4.515717443752928e-07</v>
+        <v>4.515717443752884e-07</v>
       </c>
       <c r="N16" t="n">
-        <v>7.727894796448874e-08</v>
+        <v>7.727894796448662e-08</v>
       </c>
       <c r="O16" t="n">
-        <v>1.532875944457572e-07</v>
+        <v>1.532875944457521e-07</v>
       </c>
       <c r="P16" t="n">
-        <v>1.280743900996481e-07</v>
+        <v>1.28074390099643e-07</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.261743445059195e-07</v>
+        <v>-1.261743445059246e-07</v>
       </c>
       <c r="R16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="S16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="U16" t="n">
-        <v>1.901198413486546e-07</v>
+        <v>1.901198413486502e-07</v>
       </c>
       <c r="V16" t="n">
-        <v>2.97202622272192e-07</v>
+        <v>2.972026222721854e-07</v>
       </c>
       <c r="W16" t="n">
-        <v>4.24816375139891e-07</v>
+        <v>4.248163751398834e-07</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.087700601591919e-07</v>
+        <v>-1.087700601591958e-07</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.334983910467425e-07</v>
+        <v>9.334983910467372e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>-4.025173559331397e-08</v>
+        <v>-4.025173559332053e-08</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.515717443753925e-07</v>
+        <v>4.515717443753875e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.559533475454972e-07</v>
+        <v>9.559533475454885e-07</v>
       </c>
     </row>
   </sheetData>
@@ -9970,16 +9970,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="F8" t="n">
         <v>-8.269356626531018e-07</v>
@@ -9988,16 +9988,16 @@
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="L8" t="n">
         <v>-8.269356626531018e-07</v>
@@ -10006,31 +10006,31 @@
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="O8" t="n">
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="Q8" t="n">
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="S8" t="n">
         <v>-6.954823091649584e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="U8" t="n">
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="W8" t="n">
         <v>-8.26935662653103e-07</v>
@@ -10039,13 +10039,13 @@
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="Z8" t="n">
         <v>-8.269356626531018e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>-8.269356626531024e-07</v>
+        <v>-8.269356626531023e-07</v>
       </c>
       <c r="AB8" t="n">
         <v>-8.269356626531018e-07</v>
@@ -10061,7 +10061,7 @@
         <v>-5.712199884011917e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.324716952768981e-07</v>
+        <v>-7.32471695276898e-07</v>
       </c>
       <c r="D9" t="n">
         <v>-8.529742021045185e-07</v>
@@ -10076,7 +10076,7 @@
         <v>9.609748262693772e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.705267285782646e-07</v>
+        <v>-7.705267285782647e-07</v>
       </c>
       <c r="I9" t="n">
         <v>5.721522858399524e-07</v>
@@ -10118,7 +10118,7 @@
         <v>1.252197130693313e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>5.493478706837144e-07</v>
+        <v>5.49347870683714e-07</v>
       </c>
       <c r="W9" t="n">
         <v>2.8843567126141e-06</v>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.643151080815994e-07</v>
+        <v>-3.643151080815991e-07</v>
       </c>
       <c r="C10" t="n">
         <v>3.322922112989726e-07</v>
@@ -10155,7 +10155,7 @@
         <v>3.322922112989726e-07</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.863063764235422e-08</v>
+        <v>-3.8630637642354e-08</v>
       </c>
       <c r="F10" t="n">
         <v>-2.557918291410349e-07</v>
@@ -10182,7 +10182,7 @@
         <v>3.322922112989922e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.076950010821892e-07</v>
+        <v>-2.076950010821894e-07</v>
       </c>
       <c r="O10" t="n">
         <v>-5.930182648229025e-08</v>
@@ -10677,10 +10677,10 @@
         <v>-9.019290651724016e-07</v>
       </c>
       <c r="C16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="E16" t="n">
         <v>-7.418468646034055e-07</v>
@@ -10692,19 +10692,19 @@
         <v>-5.083814355376994e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="J16" t="n">
         <v>-5.779922888477851e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="M16" t="n">
         <v>-5.595288504230842e-07</v>
@@ -10722,13 +10722,13 @@
         <v>-9.692185222746602e-07</v>
       </c>
       <c r="R16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="U16" t="n">
         <v>-7.462706246890161e-07</v>
@@ -10737,7 +10737,7 @@
         <v>-6.699972745470497e-07</v>
       </c>
       <c r="W16" t="n">
-        <v>-5.793130591367176e-07</v>
+        <v>-5.793130591367174e-07</v>
       </c>
       <c r="X16" t="n">
         <v>-9.576883624028507e-07</v>
@@ -10749,7 +10749,7 @@
         <v>-9.082893249495599e-07</v>
       </c>
       <c r="AA16" t="n">
-        <v>-5.59528850423094e-07</v>
+        <v>-5.595288504230937e-07</v>
       </c>
       <c r="AB16" t="n">
         <v>-2.018631950727467e-07</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001415309724062243</v>
+        <v>0.0001415309724062242</v>
       </c>
       <c r="C2" t="n">
-        <v>3.978891832285052e-06</v>
+        <v>3.978891832285053e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.087470475371298e-05</v>
+        <v>1.087470475371277e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>3.812674788604383e-05</v>
+        <v>3.812674788604377e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.265376448565513e-05</v>
+        <v>1.265376448565514e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.092963470232791e-05</v>
+        <v>2.092963470232771e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.505666160312248e-05</v>
+        <v>1.50566616031222e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.28271740049637e-05</v>
+        <v>1.282717400496426e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.122806123135329e-05</v>
+        <v>4.122806123135319e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.724239305377466e-06</v>
+        <v>9.724239305377311e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002087582504771756</v>
+        <v>0.0002087582504771754</v>
       </c>
       <c r="M2" t="n">
-        <v>7.651213164047717e-05</v>
+        <v>7.651213164047711e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.842837712099067e-06</v>
+        <v>4.842837712098828e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.974186600190928e-05</v>
+        <v>1.97418660019091e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.992476642360955e-05</v>
+        <v>4.992476642360936e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.581101578674027e-05</v>
+        <v>2.581101578674011e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08142510992741e-05</v>
+        <v>1.081425109927394e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>6.141097296633587e-05</v>
+        <v>6.141097296633579e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.932793893115806e-05</v>
+        <v>1.932793893115797e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.000128068654859145</v>
+        <v>0.0001280686548591451</v>
       </c>
       <c r="V2" t="n">
-        <v>3.166887055606316e-05</v>
+        <v>3.16688705560631e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.677621704820782e-05</v>
+        <v>2.677621704820781e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>6.849775717589721e-05</v>
+        <v>6.84977571758969e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.341481076396846e-05</v>
+        <v>2.341481076396788e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.363103261986438e-05</v>
+        <v>6.36310326198644e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.98863829544852e-05</v>
+        <v>4.988638295448505e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.450826488656449e-05</v>
+        <v>9.450826488656445e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.383705588489341e-06</v>
+        <v>2.383705588489876e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>3.141562506187594e-06</v>
+        <v>3.141562506187593e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.664496904566794e-06</v>
+        <v>2.664496904566791e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>2.362727365023712e-06</v>
+        <v>2.36272736502371e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.485800117817546e-06</v>
+        <v>3.485800117817339e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.227839724661988e-06</v>
+        <v>3.227839724661747e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.305424159437461e-06</v>
+        <v>3.305424159437459e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.588936512205806e-06</v>
+        <v>2.588936512205813e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.783387077203738e-06</v>
+        <v>2.783387077202753e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.735722545137829e-06</v>
+        <v>2.735722545137023e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.204316380323128e-06</v>
+        <v>2.204316380322913e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.850867384551156e-06</v>
+        <v>2.850867384551981e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.878470943619048e-06</v>
+        <v>2.878470943619047e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.296701136488984e-06</v>
+        <v>3.29670113648856e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.287977794584499e-06</v>
+        <v>2.287977794584884e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.203907111355581e-06</v>
+        <v>4.203907111355627e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.366749559799867e-06</v>
+        <v>2.36674955979971e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.296521741952855e-06</v>
+        <v>3.296521741952231e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.371183369547267e-06</v>
+        <v>4.371183369547266e-06</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.284367474167434e-05</v>
+        <v>6.284367474167426e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.260907817660036e-05</v>
+        <v>1.260907817660021e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.522099942568932e-05</v>
+        <v>1.522099942568915e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.506127893713801e-05</v>
+        <v>2.506127893713795e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.576574026080793e-05</v>
+        <v>1.576574026080788e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.888590332101082e-05</v>
+        <v>1.888590332101085e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.674527359028245e-05</v>
+        <v>1.674527359028219e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.593265154071871e-05</v>
+        <v>1.59326515407184e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.571408571830088e-05</v>
+        <v>2.571408571830108e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.480166827921837e-05</v>
+        <v>1.480166827921817e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.734722817598066e-05</v>
+        <v>8.73472281759804e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.91507283631836e-05</v>
+        <v>3.915072836318348e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.302245471877989e-05</v>
+        <v>1.302245471878078e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.845297557719252e-05</v>
+        <v>1.845297557719241e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.945428835539133e-05</v>
+        <v>2.945428835539132e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.066510940620848e-05</v>
+        <v>2.066510940620833e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.519896477852899e-05</v>
+        <v>1.519896477852883e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.364087576236814e-05</v>
+        <v>3.364087576236785e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.830210402048075e-05</v>
+        <v>1.830210402048061e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.793681807827774e-05</v>
+        <v>5.793681807827753e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.917913072380017e-05</v>
+        <v>1.91791307238002e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.101691393204798e-05</v>
+        <v>2.101691393204769e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>3.622392538953165e-05</v>
+        <v>3.622392538953111e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.979172081306816e-05</v>
+        <v>1.979172081306729e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.445006143682267e-05</v>
+        <v>3.445006143682254e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.944029803161696e-05</v>
+        <v>2.944029803161677e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.578144152133498e-05</v>
+        <v>4.57814415213349e-05</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.212612993631148e-05</v>
+        <v>1.212612993631116e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.23038814696552e-05</v>
+        <v>1.230388146965506e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.213570487316478e-05</v>
+        <v>1.213570487316467e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.201477807379678e-05</v>
+        <v>1.20147780737967e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.252783045080424e-05</v>
+        <v>1.252783045080375e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.186345120024156e-05</v>
+        <v>1.186345120024172e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.246774312290505e-05</v>
+        <v>1.246774312290501e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.220093419806293e-05</v>
+        <v>1.220093419806235e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.227180914565087e-05</v>
+        <v>1.227180914565035e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.225443598341802e-05</v>
+        <v>1.225443598341752e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.206074467642931e-05</v>
+        <v>1.206074467642983e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.229640492528522e-05</v>
+        <v>1.229640492528496e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>8.685368139005194e-06</v>
+        <v>8.685368139005185e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.245890609262232e-05</v>
+        <v>1.245890609262214e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.209123827952564e-05</v>
+        <v>1.209123827952481e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.278957201751079e-05</v>
+        <v>1.278957201751039e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.211994966296188e-05</v>
+        <v>1.21199496629618e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.245884070542046e-05</v>
+        <v>1.24588407054207e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.292753375143188e-05</v>
+        <v>1.292753375143178e-05</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.221718687464809e-05</v>
+        <v>5.221718687464796e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.982590309574084e-06</v>
+        <v>1.982590309574085e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.594511558663037e-06</v>
+        <v>4.594511558662757e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.443479107011176e-05</v>
+        <v>1.443479107011177e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.13925239378165e-06</v>
+        <v>5.139252393781656e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.230485673163225e-06</v>
+        <v>8.230485673163163e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.118785723256171e-06</v>
+        <v>6.118785723255861e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.306163673692441e-06</v>
+        <v>5.306163673692193e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.558723519480245e-05</v>
+        <v>1.558723519480235e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.175180412192102e-06</v>
+        <v>4.17518041219215e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.672074030895433e-05</v>
+        <v>7.672074030895423e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85242404961573e-05</v>
+        <v>2.852424049615728e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.395966851753612e-06</v>
+        <v>2.395966851754283e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>7.79755792934489e-06</v>
+        <v>7.797557929344897e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.879887070754373e-05</v>
+        <v>1.879887070754363e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.003862153918221e-05</v>
+        <v>1.00386215391823e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.572476911502715e-06</v>
+        <v>4.572476911502522e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>2.301438789534189e-05</v>
+        <v>2.301438789534182e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>7.675616153454489e-06</v>
+        <v>7.675616153454325e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>4.728140043043006e-05</v>
+        <v>4.728140043043008e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.204131392448831e-05</v>
+        <v>1.204131392448829e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.036149628420035e-05</v>
+        <v>1.036149628420046e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.556850774168402e-05</v>
+        <v>2.556850774168374e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.165232946041886e-06</v>
+        <v>9.165232946040884e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.382357356979644e-05</v>
+        <v>2.38235735697963e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.881381016459068e-05</v>
+        <v>1.881381016459069e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.515495365430876e-05</v>
+        <v>3.515495365430874e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.49964206928518e-06</v>
+        <v>1.499642069285028e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.677393602628928e-06</v>
+        <v>1.677393602628926e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.509217006138515e-06</v>
+        <v>1.509217006138513e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.388290206770497e-06</v>
+        <v>1.388290206770495e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.872412802956615e-06</v>
+        <v>1.872412802956419e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.736600676743158e-06</v>
+        <v>1.736600676743446e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.841255255878781e-06</v>
+        <v>1.841255255878779e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.574446331036652e-06</v>
+        <v>1.574446331036143e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.616391497803234e-06</v>
+        <v>1.616391497802732e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.599018335570405e-06</v>
+        <v>1.599018335569904e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.434256809403031e-06</v>
+        <v>1.434256809403505e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.640987277437594e-06</v>
+        <v>1.640987277437627e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5475513396933e-06</v>
+        <v>1.547551339693298e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.803488444774702e-06</v>
+        <v>1.803488444774719e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.435820631678027e-06</v>
+        <v>1.435820631677201e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.163084150484523e-06</v>
+        <v>2.163084150484367e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.493461795935609e-06</v>
+        <v>1.493461795935495e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.832352838394185e-06</v>
+        <v>1.832352838394388e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.301045884405597e-06</v>
+        <v>2.301045884405595e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.030998991095417e-06</v>
+        <v>1.030998991094948e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>9.015281074699554e-07</v>
+        <v>9.015281074699551e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.166457935030369e-06</v>
+        <v>2.166457935029865e-06</v>
       </c>
       <c r="E2" t="n">
         <v>1.158825763230114e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>2.68017839492915e-06</v>
+        <v>2.680178394929149e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.07680974815389e-06</v>
+        <v>5.076809748153435e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>9.889255839847632e-07</v>
+        <v>9.889255839842829e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.737074997149924e-06</v>
+        <v>2.737074997149431e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.567900640634564e-06</v>
+        <v>4.567900640634459e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.210870305235342e-05</v>
+        <v>1.210870305235293e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>8.011117862987435e-06</v>
+        <v>8.01111786298682e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>4.821399316224553e-06</v>
+        <v>4.821399316224549e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.237999081435437e-06</v>
+        <v>1.23799908143569e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.612019776166311e-06</v>
+        <v>1.612019776165776e-06</v>
       </c>
       <c r="P2" t="n">
         <v>1.809181352741988e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.412984871803046e-06</v>
+        <v>2.412984871802548e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.372291995578633e-06</v>
+        <v>1.372291995578134e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.232374221968319e-06</v>
+        <v>8.232374221967877e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67274446618004e-06</v>
+        <v>1.672744466179745e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48144828127066e-05</v>
+        <v>1.481448281270608e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>3.371944790621362e-06</v>
+        <v>3.371944790621361e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.116618580340938e-06</v>
+        <v>3.116618580340747e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>4.074694015122309e-05</v>
+        <v>4.074694015122261e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.536079072185435e-05</v>
+        <v>2.536079072185387e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.668721949835295e-06</v>
+        <v>1.668721949835084e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.039582197875909e-06</v>
+        <v>5.039582197875496e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.140904240997783e-06</v>
+        <v>5.140904240997781e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.39694527086545e-06</v>
+        <v>1.396945270865044e-06</v>
       </c>
       <c r="C3" t="n">
         <v>2.083929425168183e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.693842215848228e-06</v>
+        <v>1.693842215848229e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.497983060382523e-06</v>
+        <v>1.49798306038252e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.208467924126373e-06</v>
+        <v>2.208467924126365e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.062958122481339e-06</v>
+        <v>2.062958122481112e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.067365171503855e-06</v>
+        <v>2.067365171503856e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.548066194991821e-06</v>
+        <v>1.548066194991608e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.691249047495062e-06</v>
+        <v>1.691249047494702e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.656151470563377e-06</v>
+        <v>1.656151470562928e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.26485278487178e-06</v>
+        <v>1.264852784871805e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.741481598489507e-06</v>
+        <v>1.741481598489415e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.870452120089582e-06</v>
+        <v>1.870452120089579e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>2.069225687667651e-06</v>
+        <v>2.069225687667575e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.326456514020327e-06</v>
+        <v>1.326456514019896e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.738173109096164e-06</v>
+        <v>2.738173109096048e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.384459770733545e-06</v>
+        <v>1.384459770733257e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.06909359125393e-06</v>
+        <v>2.069093591253968e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.774804465779782e-06</v>
+        <v>2.774804465779783e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.651884858034972e-06</v>
+        <v>8.651884858034449e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>8.614122587940537e-06</v>
+        <v>8.61412258794064e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>9.065746309867149e-06</v>
+        <v>9.065746309866558e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.687448674661448e-06</v>
+        <v>8.687448674661557e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.25065583924714e-06</v>
+        <v>9.250655839247198e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.012653537067423e-05</v>
+        <v>1.012653537067359e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>8.63654959519396e-06</v>
+        <v>8.636549595193484e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>9.273729528485904e-06</v>
+        <v>9.273729528485377e-06</v>
       </c>
       <c r="J4" t="n">
         <v>9.442681422022507e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.268957790739488e-05</v>
+        <v>1.26895779073944e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.119605622214532e-05</v>
+        <v>1.119605622214498e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.003234283636905e-05</v>
+        <v>1.003234283636913e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>8.727333960245967e-06</v>
+        <v>8.727333960245859e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>8.863660111502796e-06</v>
+        <v>8.863660111502242e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>8.935523190976106e-06</v>
+        <v>8.935523190976152e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.155602483455374e-06</v>
+        <v>9.155602483454827e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>8.776282150504295e-06</v>
+        <v>8.776282150503731e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.127670156687073e-05</v>
+        <v>1.127670156687028e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>8.885793547947045e-06</v>
+        <v>8.885793547947028e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.367580285717358e-05</v>
+        <v>1.367580285717303e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.196389240598638e-06</v>
+        <v>6.196389240598645e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>9.412068707733229e-06</v>
+        <v>9.412068707732843e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.31278790427745e-05</v>
+        <v>2.312787904277397e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.751980824905796e-05</v>
+        <v>1.751980824905746e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.884327387974322e-06</v>
+        <v>8.884327387974152e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.011296636574561e-05</v>
+        <v>1.011296636574542e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.015218220186675e-05</v>
+        <v>1.015218220186677e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.785267979852508e-06</v>
+        <v>8.785267979852492e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>9.045093983784384e-06</v>
+        <v>9.045093983784379e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.882455889160499e-06</v>
+        <v>8.88245588916049e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>8.819759521843339e-06</v>
+        <v>8.819759521843435e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>9.081058457586179e-06</v>
+        <v>9.081058457586126e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>8.529659288675771e-06</v>
+        <v>8.52965928867574e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>9.028529730120142e-06</v>
+        <v>9.028529730120101e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>8.840349782145188e-06</v>
+        <v>8.840349782145112e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>8.892538250544657e-06</v>
+        <v>8.892538250544544e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>8.879745595889905e-06</v>
+        <v>8.87974559588948e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.737121819816292e-06</v>
+        <v>8.737121819816224e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>8.910847425521798e-06</v>
+        <v>8.910847425521724e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>5.649112793606913e-06</v>
+        <v>5.649112793606919e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>9.030306297461964e-06</v>
+        <v>9.030306297461763e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>8.759575655703503e-06</v>
+        <v>8.759575655703187e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.274129777395339e-06</v>
+        <v>9.274129777395258e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.780717161666694e-06</v>
+        <v>8.780717161666584e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.030258149870104e-06</v>
+        <v>9.030258149870167e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.289766617945999e-06</v>
+        <v>9.289766617946121e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.149716071598409e-07</v>
+        <v>6.149716071592423e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>5.772093370655448e-07</v>
+        <v>5.772093370655453e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.028833058992063e-06</v>
+        <v>1.028833058991525e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.505354237864614e-07</v>
+        <v>6.505354237864624e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.213742588372098e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.065933900174098e-06</v>
+        <v>2.06593390017343e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>5.996363443188952e-07</v>
+        <v>5.996363443183011e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.236816277610763e-06</v>
+        <v>1.236816277610175e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.878181547661969e-06</v>
+        <v>1.878181547661859e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.652664656519804e-06</v>
+        <v>4.652664656519185e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>3.159142971270287e-06</v>
+        <v>3.159142971270038e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.995429585494027e-06</v>
+        <v>1.99542958549402e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>6.904207093709663e-07</v>
+        <v>6.90420709370663e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>8.030586410025875e-07</v>
+        <v>8.030586410020773e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>8.749217204758666e-07</v>
+        <v>8.749217204759764e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.118689232580234e-06</v>
+        <v>1.118689232579635e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>7.393688996291903e-07</v>
+        <v>7.393688996285413e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.239788315995688e-06</v>
+        <v>3.239788315995073e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>8.488802970719697e-07</v>
+        <v>8.488802970718181e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>5.615201386673344e-06</v>
+        <v>5.615201386672848e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.437912157946169e-06</v>
+        <v>1.437912157946171e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.351467237233068e-06</v>
+        <v>1.351467237232668e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.506727757227431e-05</v>
+        <v>1.506727757227376e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.482894998182843e-06</v>
+        <v>9.482894998182296e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.474141370991893e-07</v>
+        <v>8.474141370989671e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.0760531148705e-06</v>
+        <v>2.076053114870399e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.115268950991669e-06</v>
+        <v>2.115268950991667e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.48354728977457e-07</v>
+        <v>7.483547289772463e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.00818073290928e-06</v>
+        <v>1.008180732909281e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>8.455426382853906e-07</v>
+        <v>8.455426382853905e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>7.828462709683451e-07</v>
+        <v>7.82846270968344e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.020456987086045e-06</v>
+        <v>1.020456987085939e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.65159414315289e-07</v>
+        <v>9.651594143150743e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.916164792450103e-07</v>
+        <v>9.916164792450038e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>8.034365312702308e-07</v>
+        <v>8.034365312699129e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>8.319367800444472e-07</v>
+        <v>8.319367800443753e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>8.191441253897714e-07</v>
+        <v>8.191441253893065e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.002085689412559e-07</v>
+        <v>7.002085689410115e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>8.502459550216297e-07</v>
+        <v>8.502459550215605e-07</v>
       </c>
       <c r="V7" t="n">
         <v>8.906357109544447e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>9.697048269617976e-07</v>
+        <v>9.69704826961603e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>6.989741852033696e-07</v>
+        <v>6.989741852030146e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.237216526520235e-06</v>
+        <v>1.23721652652002e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.438039107915959e-07</v>
+        <v>7.438039107913831e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.93344898995007e-07</v>
+        <v>9.933448989949655e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.252853367071035e-06</v>
+        <v>1.252853367071033e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001196534798286709</v>
+        <v>0.0001196534798286714</v>
       </c>
       <c r="C2" t="n">
-        <v>2.135543022959311e-06</v>
+        <v>2.135543022959397e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.187303264937222e-05</v>
+        <v>2.18730326493722e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>3.197997476376749e-05</v>
+        <v>3.197997476376789e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.270669800041376e-05</v>
+        <v>1.270669800041379e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.05990263712484e-05</v>
+        <v>2.059902637124829e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>3.544045713208395e-06</v>
+        <v>3.544045713208393e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>8.593872192303129e-06</v>
+        <v>8.593872192303111e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.792058598218188e-05</v>
+        <v>3.792058598218175e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.13391966752488e-05</v>
+        <v>1.133919667524882e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002118375120195847</v>
+        <v>0.000211837512019587</v>
       </c>
       <c r="M2" t="n">
-        <v>7.241397163526983e-05</v>
+        <v>7.241397163526979e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>7.947294930076233e-06</v>
+        <v>7.947294930076242e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.946025809707998e-05</v>
+        <v>1.946025809707996e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>6.324710783314888e-05</v>
+        <v>6.324710783314894e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.442146885266546e-05</v>
+        <v>2.442146885266549e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>3.980797713498254e-06</v>
+        <v>3.980797713498252e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>6.328304735086425e-05</v>
+        <v>6.328304735086436e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.475548807725303e-05</v>
+        <v>2.475548807725305e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001251294449426171</v>
+        <v>0.000125129444942617</v>
       </c>
       <c r="V2" t="n">
-        <v>1.914578621945035e-05</v>
+        <v>1.91457862194503e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.922719400221144e-05</v>
+        <v>1.922719400221145e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>7.474670419187715e-05</v>
+        <v>7.474670419187703e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.026662454300342e-05</v>
+        <v>2.026662454300343e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.258682882537929e-05</v>
+        <v>5.258682882537937e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.796711595888723e-05</v>
+        <v>3.796711595888737e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.18132551346054e-05</v>
+        <v>9.181325513460578e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.232328828231788e-06</v>
+        <v>2.232328828231646e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.979553440458786e-06</v>
+        <v>2.979553440458727e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.515645468236638e-06</v>
+        <v>2.515645468236641e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2351535761447e-06</v>
+        <v>2.235153576144705e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.294704947342279e-06</v>
+        <v>3.294704947342227e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="J3" t="n">
         <v>3.047811905050631e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.138086023362275e-06</v>
+        <v>3.138086023362282e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.430163429941174e-06</v>
+        <v>2.430163429941145e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.617606186526736e-06</v>
+        <v>2.617606186526527e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.571659437636624e-06</v>
+        <v>2.571659437636587e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.059404631888247e-06</v>
+        <v>2.0594046318881e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.682353329983761e-06</v>
+        <v>2.68235332998363e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.710517612889795e-06</v>
+        <v>2.710517612889855e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.112420908560278e-06</v>
+        <v>3.112420908560254e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.140050970500131e-06</v>
+        <v>2.14005097050009e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.986416733134959e-06</v>
+        <v>3.98641673313481e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.215983878252855e-06</v>
+        <v>2.215983878252728e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.112247979240444e-06</v>
+        <v>3.112247979240427e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.17197016994414e-06</v>
+        <v>4.171970169944137e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.452936177053407e-05</v>
+        <v>5.45293617705342e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.161112483256397e-05</v>
+        <v>1.161112483256392e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.888953696966042e-05</v>
+        <v>1.888953696966037e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.249200773438054e-05</v>
+        <v>2.249200773438066e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.54631941257382e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.842517664142132e-05</v>
+        <v>1.842517664142128e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.220883646125981e-05</v>
+        <v>1.220883646125978e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.404943891483347e-05</v>
+        <v>1.404943891483348e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.407146413433124e-05</v>
+        <v>2.407146413433117e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.505007745163952e-05</v>
+        <v>1.505007745163951e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.812935902456406e-05</v>
+        <v>8.812935902456443e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.732753612879596e-05</v>
+        <v>3.732753612879595e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.381376909524533e-05</v>
+        <v>1.381376909524531e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.801010897757914e-05</v>
+        <v>1.80101089775791e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.39699015352273e-05</v>
+        <v>3.396990153522728e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.981841204051201e-05</v>
+        <v>1.981841204051208e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.236802743676454e-05</v>
+        <v>1.236802743676451e-05</v>
       </c>
       <c r="S4" t="n">
         <v>3.398300106741136e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.994015812562242e-05</v>
+        <v>1.994015812562241e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.652528675253863e-05</v>
+        <v>5.652528675253865e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.361501491971251e-05</v>
+        <v>1.361501491971267e-05</v>
       </c>
       <c r="W4" t="n">
         <v>1.792515985177633e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>3.816136937290562e-05</v>
+        <v>3.816136937290581e-05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.830402007828533e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.008435501621134e-05</v>
+        <v>3.008435501621131e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.475564134971091e-05</v>
+        <v>2.475564134971095e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.447126261619207e-05</v>
+        <v>4.447126261619213e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.173073105964315e-05</v>
+        <v>1.173073105964312e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.191875671887183e-05</v>
+        <v>1.191875671887167e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.175260569378234e-05</v>
+        <v>1.175260569378233e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.164643914617491e-05</v>
+        <v>1.164643914617489e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.21179546800087e-05</v>
+        <v>1.211795468000863e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.136074748000473e-05</v>
+        <v>1.13607474800047e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.207728930177533e-05</v>
+        <v>1.207728930177529e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.180283944887504e-05</v>
+        <v>1.180283944887499e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.187116013258651e-05</v>
+        <v>1.187116013258638e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.185441308215003e-05</v>
+        <v>1.18544130821499e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.166770222065436e-05</v>
+        <v>1.166770222065433e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.189475970607725e-05</v>
+        <v>1.189475970607715e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>7.624552505288964e-06</v>
+        <v>7.62455250528898e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.205151428835992e-05</v>
+        <v>1.205151428835988e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.169709686408129e-05</v>
+        <v>1.169709686408128e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.237007550344026e-05</v>
+        <v>1.237007550344008e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.172477351730794e-05</v>
+        <v>1.172477351730784e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.205145125765348e-05</v>
+        <v>1.205145125765333e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.252704338249992e-05</v>
+        <v>1.252704338249991e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.417921429421224e-05</v>
+        <v>4.417921429421239e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.260977356242148e-06</v>
+        <v>1.260977356242152e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>8.539389493338609e-06</v>
+        <v>8.539389493338511e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.214186025805874e-05</v>
+        <v>1.214186025805888e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.113046649416387e-06</v>
+        <v>5.113046649416402e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.046684496630625e-06</v>
+        <v>8.04668449663057e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.858688984937993e-06</v>
+        <v>1.85868898493789e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>3.699291438511674e-06</v>
+        <v>3.699291438511577e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.432105687642094e-05</v>
+        <v>1.432105687642086e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.699929975317707e-06</v>
+        <v>4.699929975317619e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.777921154824211e-05</v>
+        <v>7.777921154824233e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.697738865247416e-05</v>
+        <v>2.697738865247411e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.463621618923514e-06</v>
+        <v>3.463621618923427e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>7.631616832788435e-06</v>
+        <v>7.631616832788411e-06</v>
       </c>
       <c r="P6" t="n">
         <v>2.359140939043656e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.468264564190225e-06</v>
+        <v>9.468264564190132e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>2.017879960442726e-06</v>
+        <v>2.017879960442626e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>2.363285359108958e-05</v>
+        <v>2.36328535910895e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>9.590010649300633e-06</v>
+        <v>9.590010649300558e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>4.614679460774786e-05</v>
+        <v>4.61467946077479e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>7.418280506367362e-06</v>
+        <v>7.418280506367279e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>7.54666770698563e-06</v>
+        <v>7.546667706985648e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.778287722811489e-05</v>
+        <v>2.778287722811499e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.953872601963539e-06</v>
+        <v>7.953872601963446e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.973420753988955e-05</v>
+        <v>1.973420753988959e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.44054938733891e-05</v>
+        <v>1.440549387338906e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.412111513987025e-05</v>
+        <v>3.41211151398703e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.380583583321348e-06</v>
+        <v>1.380583583321194e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.568609242550003e-06</v>
+        <v>1.568609242549775e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.402458217460531e-06</v>
+        <v>1.402458217460535e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.296291669853096e-06</v>
+        <v>1.2962916698531e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.739462535218008e-06</v>
+        <v>1.739462535217949e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.61034022209443e-06</v>
+        <v>1.610340222094389e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.727141825453509e-06</v>
+        <v>1.727141825453515e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.452691972553237e-06</v>
+        <v>1.452691972553119e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.492667987795823e-06</v>
+        <v>1.492667987795698e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.475920937359344e-06</v>
+        <v>1.475920937359237e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.317554744332559e-06</v>
+        <v>1.317554744332387e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.516267561286555e-06</v>
+        <v>1.516267561286486e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.427818091943802e-06</v>
+        <v>1.427818091943877e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.673022143569219e-06</v>
+        <v>1.673022143569215e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.318604719290598e-06</v>
+        <v>1.31860471929061e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.019928027118448e-06</v>
+        <v>2.019928027118341e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.374626040986129e-06</v>
+        <v>1.37462604098604e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.701303781331668e-06</v>
+        <v>1.70130378133164e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.176895906178118e-06</v>
+        <v>2.176895906178121e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.782240757138646e-05</v>
+        <v>9.782240757138674e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.20546076654328e-06</v>
+        <v>2.205460766543281e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.982291383554131e-05</v>
+        <v>2.982291383554135e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.550142432573823e-05</v>
+        <v>2.55014243257382e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.967426048859653e-05</v>
+        <v>1.967426048859654e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.078709788081627e-05</v>
+        <v>2.078709788081633e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.656251500636329e-06</v>
+        <v>1.656251500636328e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.376378651028552e-05</v>
+        <v>3.376378651028551e-05</v>
       </c>
       <c r="J2" t="n">
         <v>3.985616050410939e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.377742219642056e-05</v>
+        <v>5.377742219642063e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001904338512660177</v>
+        <v>0.0001904338512660173</v>
       </c>
       <c r="M2" t="n">
-        <v>6.654836658756749e-05</v>
+        <v>6.654836658756751e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.090517871853235e-05</v>
+        <v>1.090517871853234e-05</v>
       </c>
       <c r="O2" t="n">
         <v>1.857667423913612e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>6.403071868932742e-05</v>
+        <v>6.403071868932754e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.495357658384468e-05</v>
+        <v>2.49535765838447e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>3.499237875897739e-06</v>
+        <v>3.499237875897738e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>6.157683204438616e-05</v>
+        <v>6.157683204438609e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.865975613314785e-05</v>
+        <v>2.865975613314786e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001306434298153738</v>
+        <v>0.0001306434298153737</v>
       </c>
       <c r="V2" t="n">
-        <v>3.01725294588984e-05</v>
+        <v>3.017252945889854e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.592196947327552e-05</v>
+        <v>2.592196947327548e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00010345010014577</v>
+        <v>0.0001034501001457699</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.022642896204905e-05</v>
+        <v>4.022642896204903e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.414007901046991e-05</v>
+        <v>5.414007901046996e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.12166831865059e-05</v>
+        <v>4.121668318650585e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.808212897536435e-05</v>
+        <v>8.808212897536434e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.309695110195816e-06</v>
+        <v>2.309695110195892e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>3.065049193328108e-06</v>
+        <v>3.06504919332811e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.581484362408247e-06</v>
+        <v>2.58148436240825e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>2.332819194144164e-06</v>
+        <v>2.332819194144166e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.388051027174162e-06</v>
+        <v>3.388051027174227e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.14289926648373e-06</v>
+        <v>3.142899266483821e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.206793625909323e-06</v>
+        <v>3.206793625909325e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.510505453620323e-06</v>
+        <v>2.510505453620381e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.700767642315357e-06</v>
+        <v>2.700767642315486e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65412978249089e-06</v>
+        <v>2.654129782490931e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.134169863580535e-06</v>
+        <v>2.134169863580633e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.767170300360763e-06</v>
+        <v>2.767170300360959e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.812231603981673e-06</v>
+        <v>2.812231603981759e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.203025151405866e-06</v>
+        <v>3.203025151405942e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.216029249190799e-06</v>
+        <v>2.216029249190896e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.09133328691598e-06</v>
+        <v>4.091333286915921e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.293104306616429e-06</v>
+        <v>2.293104306616433e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.202849621001356e-06</v>
+        <v>3.202849621001377e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.257207372007778e-06</v>
+        <v>4.257207372007745e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2814,82 +2814,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.670680213029538e-05</v>
+        <v>4.67068021302954e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176797402088598e-05</v>
+        <v>1.1767974020886e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192178515394926e-05</v>
+        <v>2.192178515394927e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.025400373200226e-05</v>
+        <v>2.025400373200227e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.81489887752053e-05</v>
+        <v>1.814898877520533e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.862833634235988e-05</v>
+        <v>1.862833634235991e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.165536748252438e-05</v>
+        <v>1.165536748252436e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.335818696783022e-05</v>
+        <v>2.335818696783019e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.502413586444072e-05</v>
+        <v>2.50241358644408e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.065292216345094e-05</v>
+        <v>3.065292216345092e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.046258585851096e-05</v>
+        <v>8.046258585851089e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.53102878914555e-05</v>
+        <v>3.531028789145551e-05</v>
       </c>
       <c r="N4" t="n">
         <v>1.502649284706076e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.78226628810723e-05</v>
+        <v>1.782266288107231e-05</v>
       </c>
       <c r="P4" t="n">
         <v>3.439012833482933e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.014696890435067e-05</v>
+        <v>2.014696890435068e-05</v>
       </c>
       <c r="R4" t="n">
         <v>1.23271143748685e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.349571546774e-05</v>
+        <v>3.349571546773998e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.149782782991411e-05</v>
+        <v>2.149782782991416e-05</v>
       </c>
       <c r="U4" t="n">
         <v>5.866967933432714e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.850963474082714e-05</v>
+        <v>1.85096347408275e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04999367411048e-05</v>
+        <v>2.049993674110478e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.875802998995541e-05</v>
+        <v>4.875802998995535e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.571374425331893e-05</v>
+        <v>2.571374425331891e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.078510631364066e-05</v>
+        <v>3.078510631364064e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.607468028998127e-05</v>
+        <v>2.607468028998123e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>4.323372539451062e-05</v>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.189354000508653e-05</v>
+        <v>1.189354000508656e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.208128390865211e-05</v>
+        <v>1.208128390865214e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.18999547548918e-05</v>
+        <v>1.189995475489181e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.182823705686211e-05</v>
+        <v>1.182823705686214e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.228658807413063e-05</v>
+        <v>1.228658807413077e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.164258325220541e-05</v>
+        <v>1.164258325220547e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.222302834123338e-05</v>
+        <v>1.22230283412334e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.196673301723067e-05</v>
+        <v>1.196673301723078e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.203608135083863e-05</v>
+        <v>1.20360813508387e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.201908239858196e-05</v>
+        <v>1.201908239858197e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.182956311381677e-05</v>
+        <v>1.182956311381679e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.206028433995674e-05</v>
+        <v>1.206028433995683e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>8.537127453548178e-06</v>
+        <v>8.537127453548142e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.221914831509666e-05</v>
+        <v>1.221914831509676e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.185939989863031e-05</v>
+        <v>1.18593998986304e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25429261994493e-05</v>
+        <v>1.254292619944927e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.188749285200092e-05</v>
+        <v>1.188749285200095e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.221908433632537e-05</v>
+        <v>1.221908433632547e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.268052579201293e-05</v>
+        <v>1.268052579201294e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.625925927483688e-05</v>
+        <v>3.625925927483692e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.320431165427561e-06</v>
+        <v>1.320431165427564e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.147424229849083e-05</v>
+        <v>1.147424229849084e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.80646087654383e-06</v>
+        <v>9.806460876543818e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.701445919746891e-06</v>
+        <v>7.701445919746892e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.151163605768183e-06</v>
+        <v>8.151163605768163e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.207824627065944e-06</v>
+        <v>1.207824627065927e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.291064411237176e-05</v>
+        <v>1.291064411237174e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.506539950759851e-05</v>
+        <v>1.506539950759863e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.020537930799252e-05</v>
+        <v>2.020537930799254e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>7.001504300305263e-05</v>
+        <v>7.001504300305256e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.486274503599705e-05</v>
+        <v>2.486274503599709e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.578949991602337e-06</v>
+        <v>4.578949991602321e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>7.345490144480618e-06</v>
+        <v>7.3454901444806e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>2.391295559823761e-05</v>
+        <v>2.391295559823758e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.699426048892248e-06</v>
+        <v>9.699426048892234e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.879571519410096e-06</v>
+        <v>1.879571519410062e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>2.30481726122816e-05</v>
+        <v>2.304817261228157e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.105028497445573e-05</v>
+        <v>1.105028497445572e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>4.81925065977355e-05</v>
+        <v>4.819250659773544e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.148233767400545e-05</v>
+        <v>1.148233767400556e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.002276400451309e-05</v>
+        <v>1.002276400451305e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>3.828085725336371e-05</v>
+        <v>3.828085725336367e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.526620139786049e-05</v>
+        <v>1.526620139786048e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.033756345818223e-05</v>
+        <v>2.033756345818217e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.56271374345228e-05</v>
+        <v>1.562713743452278e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.278618253905225e-05</v>
+        <v>3.278618253905223e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.445997149628141e-06</v>
+        <v>1.445997149628125e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.633741053193708e-06</v>
+        <v>1.633741053193711e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.452411899433373e-06</v>
+        <v>1.452411899433376e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.380694201403695e-06</v>
+        <v>1.380694201403697e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.809415337538919e-06</v>
+        <v>1.809415337539028e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.683846895363273e-06</v>
+        <v>1.683846895363298e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.775485485774966e-06</v>
+        <v>1.775485485774969e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.51919016177223e-06</v>
+        <v>1.519190161772357e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55890861424692e-06</v>
+        <v>1.558908614246977e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.541909661990255e-06</v>
+        <v>1.541909661990245e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.382020258358384e-06</v>
+        <v>1.382020258358369e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.583111603365053e-06</v>
+        <v>1.583111603365101e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.509830386726489e-06</v>
+        <v>1.509830386726532e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.741975578504942e-06</v>
+        <v>1.741975578505026e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.382227162038598e-06</v>
+        <v>1.382227162038667e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.095383343990874e-06</v>
+        <v>2.095383343990843e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.439949996542483e-06</v>
+        <v>1.439949996542517e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.771541480866942e-06</v>
+        <v>1.771541480867035e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.232982936554519e-06</v>
+        <v>2.232982936554498e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.361228054036276e-05</v>
+        <v>8.361228054036263e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>3.630805887471075e-06</v>
+        <v>3.630805887471073e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.692907987035427e-05</v>
+        <v>2.692907987035418e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.89372745381107e-05</v>
+        <v>1.893727453811071e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.276392136224743e-05</v>
+        <v>2.276392136224744e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.035382995532168e-05</v>
+        <v>2.035382995532162e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.865927591755102e-06</v>
+        <v>1.865927591754943e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.758014447910362e-05</v>
+        <v>3.758014447910341e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.067210646263499e-05</v>
+        <v>4.06721064626349e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.263246438122055e-05</v>
+        <v>6.263246438122044e-05</v>
       </c>
       <c r="L2" t="n">
         <v>0.0001567181171912087</v>
       </c>
       <c r="M2" t="n">
-        <v>5.958605885312563e-05</v>
+        <v>5.958605885312598e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.620312852358295e-06</v>
+        <v>9.620312852358129e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.311500709392599e-05</v>
+        <v>1.311500709392581e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>5.916820260331497e-05</v>
+        <v>5.916820260331481e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.239157109912504e-05</v>
+        <v>3.239157109912481e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>9.057806884477697e-06</v>
+        <v>9.057806884477533e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>5.793091209096915e-05</v>
+        <v>5.793091209096904e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.945054252321895e-05</v>
+        <v>2.945054252321881e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001469572122683626</v>
+        <v>0.0001469572122683625</v>
       </c>
       <c r="V2" t="n">
-        <v>5.438149093719464e-05</v>
+        <v>5.438149093719452e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.092811981226682e-05</v>
+        <v>3.092811981226665e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0001169345115766681</v>
+        <v>0.0001169345115766679</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.466077729164929e-05</v>
+        <v>6.466077729164936e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.284898100546364e-05</v>
+        <v>5.284898100546351e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.401507269032626e-05</v>
+        <v>4.401507269032609e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.369526064661348e-05</v>
+        <v>8.369526064661373e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.409067581554318e-06</v>
+        <v>2.409067581554261e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>3.193463030214428e-06</v>
+        <v>3.193463030214427e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.682406421790033e-06</v>
+        <v>2.682406421790031e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>2.450414661926363e-06</v>
+        <v>2.45041466192636e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>3.512681335981917e-06</v>
+        <v>3.512681335981749e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>3.281502837917876e-06</v>
+        <v>3.281502837917877e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.311688291962703e-06</v>
+        <v>3.311688291962951e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.614581413802009e-06</v>
+        <v>2.61458141380197e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.809300026710185e-06</v>
+        <v>2.809300026709992e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.76156978963078e-06</v>
+        <v>2.761569789630583e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.229431087374081e-06</v>
+        <v>2.229431087374028e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.879025867690518e-06</v>
+        <v>2.87902586769037e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.976199155484507e-06</v>
+        <v>2.976199155484474e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.323321683715908e-06</v>
+        <v>3.323321683715789e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>2.313207827913513e-06</v>
+        <v>2.313207827913474e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.235460555116751e-06</v>
+        <v>4.235460555116643e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.392088179173485e-06</v>
+        <v>2.392088179173331e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.323142041978004e-06</v>
+        <v>3.323142041977855e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.388212433811792e-06</v>
+        <v>4.388212433811789e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.155053220233192e-05</v>
+        <v>4.155053220233183e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.23158113465024e-05</v>
+        <v>1.231581134650237e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.089017116586119e-05</v>
+        <v>2.089017116586107e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.787937176144026e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.930779813641307e-05</v>
+        <v>1.930779813641302e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.849356978231448e-05</v>
+        <v>1.849356978231442e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.175494646670473e-05</v>
+        <v>1.175494646670463e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.477235914463509e-05</v>
+        <v>2.477235914463498e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.562629863282347e-05</v>
+        <v>2.562629863282342e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.390363556976394e-05</v>
+        <v>3.390363556976386e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>6.819675120948985e-05</v>
+        <v>6.819675120948986e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.278597753484192e-05</v>
+        <v>3.278597753484215e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.45813288376056e-05</v>
+        <v>1.458132883760551e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.585510385188538e-05</v>
+        <v>1.585510385188527e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.264095283113297e-05</v>
+        <v>3.264095283113292e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.288118507493759e-05</v>
+        <v>2.288118507493748e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.437630201759169e-05</v>
+        <v>1.437630201759159e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.218997496838172e-05</v>
+        <v>3.218997496838152e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.180921469432103e-05</v>
+        <v>2.180921469432093e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>6.463901598344498e-05</v>
+        <v>6.463901598344492e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>2.918798005375086e-05</v>
+        <v>2.918798005375104e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.234777426559043e-05</v>
+        <v>2.234777426559033e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>5.36960941256729e-05</v>
+        <v>5.369609412567282e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.464293180796259e-05</v>
+        <v>3.464293180796251e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.033767076276264e-05</v>
+        <v>3.033767076276249e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.711781491488369e-05</v>
+        <v>2.71178149148836e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.165083831484684e-05</v>
+        <v>4.16508383148469e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.195291461511486e-05</v>
+        <v>1.195291461511472e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.215640501057149e-05</v>
+        <v>1.215640501057147e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.195466320733965e-05</v>
+        <v>1.195466320733962e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190376347738471e-05</v>
+        <v>1.19037634773847e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.235516886931671e-05</v>
+        <v>1.235516886931654e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.199786267424918e-05</v>
+        <v>1.199786267424914e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.227463027231987e-05</v>
+        <v>1.227463027232008e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.202782199370389e-05</v>
+        <v>1.202782199370375e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.209879464160745e-05</v>
+        <v>1.209879464160734e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.20813975306687e-05</v>
+        <v>1.208139753066861e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.188743922238442e-05</v>
+        <v>1.188743922238423e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.212420889188266e-05</v>
+        <v>1.21242088918825e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.045135483072959e-05</v>
+        <v>1.045135483072989e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228614949963907e-05</v>
+        <v>1.228614949963891e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.191797486055479e-05</v>
+        <v>1.191797486055471e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.261861340738919e-05</v>
+        <v>1.261861340738912e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.19467258223292e-05</v>
+        <v>1.194672582232908e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.228608402233498e-05</v>
+        <v>1.228608402233489e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.274435051165852e-05</v>
+        <v>1.27443505116585e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.112365918053915e-05</v>
+        <v>3.112365918053898e-05</v>
       </c>
       <c r="C6" t="n">
         <v>1.888938324709597e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.04632981440684e-05</v>
+        <v>1.046329814406829e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>7.452498739647434e-06</v>
+        <v>7.452498739647441e-06</v>
       </c>
       <c r="F6" t="n">
         <v>8.880925114620251e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.035470897592665e-06</v>
+        <v>8.035470897592423e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.328073444911965e-06</v>
+        <v>1.328073444911832e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.434548612284233e-05</v>
+        <v>1.434548612284221e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.541678023997543e-05</v>
+        <v>1.541678023997537e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.347676254797119e-05</v>
+        <v>2.347676254797109e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.776987818769719e-05</v>
+        <v>5.776987818769708e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.23591045130491e-05</v>
+        <v>2.235910451304907e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.154455815812843e-06</v>
+        <v>4.154455815812716e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>5.397004967163452e-06</v>
+        <v>5.397004967163289e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>2.218285394641103e-05</v>
+        <v>2.218285394641091e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.245431205314484e-05</v>
+        <v>1.24543120531447e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.949428995798927e-06</v>
+        <v>3.949428995798795e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>2.176310194658899e-05</v>
+        <v>2.176310194658878e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.138234167252827e-05</v>
+        <v>1.138234167252813e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.418091709872306e-05</v>
+        <v>5.418091709872296e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>2.037881533487505e-05</v>
+        <v>2.037881533487501e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18896753808685e-05</v>
+        <v>1.188967538086833e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>4.323799524095094e-05</v>
+        <v>4.323799524095088e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.421605878616982e-05</v>
+        <v>2.421605878616971e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.991079774096987e-05</v>
+        <v>1.991079774096968e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.669094189309092e-05</v>
+        <v>1.669094189309079e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.122396529305402e-05</v>
+        <v>3.122396529305399e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.526041593321979e-06</v>
+        <v>1.526041593321921e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.729531988778662e-06</v>
+        <v>1.729531988778659e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.527790185546814e-06</v>
+        <v>1.527790185546811e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.47689045559192e-06</v>
+        <v>1.476890455591917e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.897069984594636e-06</v>
+        <v>1.897069984594545e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.788344281401089e-06</v>
+        <v>1.788344281401074e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.847757250527056e-06</v>
+        <v>1.847757250527026e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.600948971911011e-06</v>
+        <v>1.600948971910951e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.640695756885454e-06</v>
+        <v>1.640695756885325e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.623298645946757e-06</v>
+        <v>1.623298645946624e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.460566200591539e-06</v>
+        <v>1.460566200591438e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.666110007160747e-06</v>
+        <v>1.666110007160511e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.642190111853814e-06</v>
+        <v>1.642190111853837e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.828050614916996e-06</v>
+        <v>1.8280506149169e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.459875975832838e-06</v>
+        <v>1.459875975832705e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.191740385596466e-06</v>
+        <v>2.191740385596322e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.519852800536429e-06</v>
+        <v>1.51985280053628e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.859211000542262e-06</v>
+        <v>1.85921100054209e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.317477489865705e-06</v>
+        <v>2.317477489865702e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4009,79 +4009,79 @@
         <v>1.15220842637365e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>7.577965366176597e-07</v>
+        <v>7.577965366176575e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.27691006493435e-06</v>
+        <v>2.276910064934361e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>3.724416842478811e-06</v>
+        <v>3.724416842478816e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.534818214689729e-06</v>
+        <v>1.53481821468973e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.836696495527381e-06</v>
+        <v>7.836696495527386e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>2.054579397590247e-06</v>
+        <v>2.054579397590256e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.642979422052834e-06</v>
+        <v>2.64297942205285e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.866190828963784e-06</v>
+        <v>9.866190828963795e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.354643020250142e-06</v>
+        <v>6.354643020250155e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.59898822700991e-05</v>
+        <v>4.598988227009907e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.29636947691625e-05</v>
+        <v>2.296369476916249e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.280316162957418e-06</v>
+        <v>1.280316162957409e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>2.351504351059893e-06</v>
+        <v>2.351504351059914e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.270030137213445e-05</v>
+        <v>1.270030137213446e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.444547029372877e-06</v>
+        <v>3.444547029372857e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.048155924843455e-06</v>
+        <v>1.04815592484347e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>7.900169675438185e-06</v>
+        <v>7.900169675438197e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>2.710500961946194e-06</v>
+        <v>2.710500961946204e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>5.286059918056247e-05</v>
+        <v>5.286059918056258e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>4.344360980216396e-06</v>
+        <v>4.344360980216389e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.294814525645962e-05</v>
+        <v>1.294814525645965e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.180221766233349e-05</v>
+        <v>1.180221766233352e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.111332401791362e-06</v>
+        <v>3.111332401791381e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.824141407931696e-06</v>
+        <v>9.824141407931733e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.797216882303356e-05</v>
+        <v>1.797216882303355e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>2.987477725400027e-05</v>
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.495548689221038e-06</v>
+        <v>1.495548689221062e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.184604513473906e-06</v>
+        <v>2.184604513473905e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="E3" t="n">
         <v>1.784718851432023e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.573454046369674e-06</v>
+        <v>1.573454046369671e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.334952973868291e-06</v>
+        <v>2.334952973868336e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.176969353963041e-06</v>
+        <v>2.176969353963045e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.217422384919401e-06</v>
+        <v>2.217422384919403e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.651861702424736e-06</v>
+        <v>1.651861702424748e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.799963914236489e-06</v>
+        <v>1.799963914236511e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.763660483469127e-06</v>
+        <v>1.763660483469148e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.358917877660613e-06</v>
+        <v>1.358917877660623e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="U3" t="n">
         <v>1.85173823522518e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.963328399240494e-06</v>
+        <v>1.963328399240481e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>2.190926766579744e-06</v>
+        <v>2.190926766579771e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.422638137341865e-06</v>
+        <v>1.422638137341876e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.882542430781244e-06</v>
+        <v>2.882542430781249e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.482634222489704e-06</v>
+        <v>1.482634222489714e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.190790131693071e-06</v>
+        <v>2.1907901316931e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.984332399169921e-06</v>
+        <v>2.984332399169913e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.285106018240247e-05</v>
+        <v>1.285106018240248e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>8.923672673502377e-06</v>
+        <v>8.923672673502385e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>9.481302749255613e-06</v>
+        <v>9.481302749255634e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.986102530548131e-06</v>
+        <v>9.986102530548129e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.191496164146619e-06</v>
+        <v>9.191496164146626e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.150777961689834e-05</v>
+        <v>1.150777961689835e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>9.40026583174719e-06</v>
+        <v>9.400265831747226e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>9.614730731321884e-06</v>
+        <v>9.61473073132194e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.170974306921921e-05</v>
+        <v>1.170974306921922e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.096758852831035e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.541416781440294e-05</v>
+        <v>2.541416781440295e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>1.70383179671135e-05</v>
+        <v>1.703831796711349e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>9.118055974581462e-06</v>
+        <v>9.118055974581469e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.508491490618038e-06</v>
+        <v>9.508491490618042e-06</v>
       </c>
       <c r="P4" t="n">
         <v>1.328050648308973e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.906892711707975e-06</v>
+        <v>9.906892711707992e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>9.03343629395207e-06</v>
+        <v>9.033436293952084e-06</v>
       </c>
       <c r="S4" t="n">
         <v>1.153091484563613e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>9.639341539735062e-06</v>
+        <v>9.63934153973506e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>2.791846344823551e-05</v>
+        <v>2.791846344823552e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>6.681648134274002e-06</v>
+        <v>6.681648134274006e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.337084266859644e-05</v>
+        <v>1.337084266859645e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.295316551669862e-05</v>
+        <v>1.295316551669865e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.785439892758223e-06</v>
+        <v>9.785439892758228e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.223217994971327e-05</v>
+        <v>1.223217994971329e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.520204026354938e-05</v>
+        <v>1.520204026354939e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.958317403469357e-05</v>
+        <v>1.958317403469354e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.196505703016614e-06</v>
+        <v>9.196505703016668e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>9.443727426641313e-06</v>
+        <v>9.443727426641318e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>9.279105389895353e-06</v>
+        <v>9.27910538989536e-06</v>
       </c>
       <c r="F5" t="n">
         <v>9.205578471109124e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>9.502458707987792e-06</v>
+        <v>9.502458707987819e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>8.90711213297861e-06</v>
+        <v>8.907112132978612e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>9.476545298086823e-06</v>
+        <v>9.476545298086837e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>9.253479960809289e-06</v>
+        <v>9.253479960809301e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>9.307461477910719e-06</v>
+        <v>9.307461477910746e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>9.294229303692409e-06</v>
+        <v>9.294229303692421e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.146705376602836e-06</v>
+        <v>9.146705376602856e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>9.326332609946303e-06</v>
+        <v>9.326332609946308e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>5.813789718004471e-06</v>
+        <v>5.813789718004479e-06</v>
       </c>
       <c r="W5" t="n">
         <v>9.449962846672234e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>9.169930663015607e-06</v>
+        <v>9.169930663015591e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.702048634912518e-06</v>
+        <v>9.702048634912539e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.191798531542374e-06</v>
+        <v>9.191798531542416e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.449913044860481e-06</v>
+        <v>9.449913044860499e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.781922648653603e-06</v>
+        <v>9.781922648653627e-06</v>
       </c>
     </row>
     <row r="6">
@@ -4358,82 +4358,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.478675269900972e-06</v>
+        <v>4.47867526990097e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.512877610008698e-07</v>
+        <v>5.512877610008694e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.108917836754115e-06</v>
+        <v>1.108917836754117e-06</v>
       </c>
       <c r="E6" t="n">
         <v>1.613717618046624e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>8.191112516451153e-07</v>
+        <v>8.191112516451167e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>3.111446237914988e-06</v>
+        <v>3.111446237914973e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.027880919245692e-06</v>
+        <v>1.027880919245722e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.242345818820379e-06</v>
+        <v>1.242345818820415e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.844037562026728e-06</v>
+        <v>3.844037562026748e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>2.595203615808836e-06</v>
+        <v>2.595203615808844e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.704178290190142e-05</v>
+        <v>1.704178290190141e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>8.665933054611985e-06</v>
+        <v>8.66593305461198e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>7.456710620799543e-07</v>
+        <v>7.456710620799521e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.112158111634691e-06</v>
+        <v>1.112158111634701e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>4.884173104106379e-06</v>
+        <v>4.884173104106382e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.534507799206472e-06</v>
+        <v>1.534507799206483e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>6.610513814505688e-07</v>
+        <v>6.610513814505745e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.158529933134618e-06</v>
+        <v>3.158529933134629e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>1.266956627233556e-06</v>
+        <v>1.266956627233559e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.952213006925216e-05</v>
+        <v>1.952213006925218e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.817739924223359e-06</v>
+        <v>1.817739924223361e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>4.974509289613074e-06</v>
+        <v>4.974509289613076e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>4.556832137715286e-06</v>
+        <v>4.556832137715296e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.413054980256716e-06</v>
+        <v>1.413054980256737e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.859795037211773e-06</v>
+        <v>3.859795037211782e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.82965535104787e-06</v>
+        <v>6.829655351047853e-06</v>
       </c>
       <c r="AB6" t="n">
         <v>1.121078912219205e-05</v>
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.241207905151234e-07</v>
+        <v>8.241207905151547e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.071342514139811e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>9.067204773938471e-07</v>
+        <v>9.067204773938451e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>8.331935586076134e-07</v>
+        <v>8.331935586076136e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.106125329004435e-06</v>
+        <v>1.106125329004463e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.041406625786138e-06</v>
+        <v>1.041406625786137e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.104160385585318e-06</v>
+        <v>1.104160385585319e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>8.810950483077944e-07</v>
+        <v>8.810950483077898e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.111280989273511e-07</v>
+        <v>9.111280989273801e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>8.978959247090555e-07</v>
+        <v>8.97895924709062e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.743204641013354e-07</v>
+        <v>7.743204641013481e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>9.299992309629575e-07</v>
+        <v>9.299992309629477e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>9.498815079538247e-07</v>
+        <v>9.498815079538212e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.053629467688874e-06</v>
+        <v>1.053629467688876e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>7.735972840322391e-07</v>
+        <v>7.735972840322213e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.329663722411009e-06</v>
+        <v>1.329663722411032e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.194136190408697e-07</v>
+        <v>8.19413619040892e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07752813235898e-06</v>
+        <v>1.077528132358984e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.409537736152099e-06</v>
+        <v>1.409537736152101e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.133512148235088e-06</v>
+        <v>1.133512148235016e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.000563199832015e-06</v>
+        <v>1.000563199832422e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.713427708672747e-07</v>
+        <v>8.713427708672046e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.122432266515226e-06</v>
+        <v>1.122432266515224e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.314141060661083e-06</v>
+        <v>1.314141060661082e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.559203552415383e-06</v>
+        <v>2.559203552415223e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>9.480592909711658e-07</v>
+        <v>9.480592909710938e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.197408206070273e-06</v>
+        <v>2.197408206070207e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.518433270752152e-06</v>
+        <v>2.518433270752099e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.084160373735663e-06</v>
+        <v>4.084160373735589e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>2.329719365011491e-06</v>
+        <v>2.329719365011417e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.633112681467542e-06</v>
+        <v>2.633112681467538e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>8.590901393424195e-07</v>
+        <v>8.590901393423563e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.192032526458117e-06</v>
+        <v>1.192032526458046e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>6.964496290083585e-07</v>
+        <v>6.964496290082907e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.263589533924511e-07</v>
+        <v>9.263589533923872e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.158238999629718e-06</v>
+        <v>1.158238999629643e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>4.016020570434342e-06</v>
+        <v>4.016020570434268e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>8.528899072420979e-07</v>
+        <v>8.528899072421127e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.830182890125667e-06</v>
+        <v>2.830182890125596e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>2.162504310769946e-06</v>
+        <v>2.162504310769833e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>4.348890474771228e-06</v>
+        <v>4.348890474771152e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>2.061344169963826e-05</v>
+        <v>2.061344169963816e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.679813614620356e-06</v>
+        <v>9.679813614620272e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.850698894628827e-06</v>
+        <v>1.850698894628753e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.142077645540199e-06</v>
+        <v>4.142077645540131e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.32308760566945e-06</v>
+        <v>2.323087605669445e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.326034996198125e-06</v>
+        <v>1.326034996198145e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.991314985800507e-06</v>
+        <v>1.991314985799242e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.615246416646272e-06</v>
+        <v>1.615246416646262e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.421716825223608e-06</v>
+        <v>1.421716825223602e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.108626459119456e-06</v>
+        <v>2.108626459119455e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.968633647522789e-06</v>
+        <v>1.968633647522723e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>1.969302861514667e-06</v>
+        <v>1.969302861514657e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.471768383449434e-06</v>
+        <v>1.471768383449426e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.609846695319693e-06</v>
+        <v>1.60984669531955e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.576000364639762e-06</v>
+        <v>1.576000364639733e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.198651673699859e-06</v>
+        <v>1.19865167369991e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.658286738671658e-06</v>
+        <v>1.658286738671618e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.78385899158363e-06</v>
+        <v>1.783858991583549e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.974348278356176e-06</v>
+        <v>1.974348278356052e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.25805919895278e-06</v>
+        <v>1.2580591989527e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.619444493642509e-06</v>
+        <v>2.619444493642424e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.313994610419196e-06</v>
+        <v>1.313994610419199e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.974220891242697e-06</v>
+        <v>1.974220891242551e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.648101435516297e-06</v>
+        <v>2.648101435516283e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.52573861506736e-06</v>
+        <v>8.525738615067302e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>8.488143782360307e-06</v>
+        <v>8.488143782358504e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>8.430180955565047e-06</v>
+        <v>8.430180955564983e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.512908073865098e-06</v>
+        <v>8.512908073865096e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>8.588208818127194e-06</v>
+        <v>8.588208818127174e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>9.045386390577356e-06</v>
+        <v>9.045386390577287e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.45814322629205e-06</v>
+        <v>8.458143226291984e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>8.913516235250037e-06</v>
+        <v>8.913516235249975e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.535791834331742e-06</v>
+        <v>8.535791834331725e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>9.601215245001532e-06</v>
+        <v>9.60121524500148e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>8.961742099008046e-06</v>
+        <v>8.961742099007981e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>9.069199934589493e-06</v>
+        <v>9.0691999345895e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>8.425715015251925e-06</v>
+        <v>8.425715015251854e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>8.547068605748688e-06</v>
+        <v>8.547068605748622e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>8.366434459056427e-06</v>
+        <v>8.366434459056377e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.45023370806285e-06</v>
+        <v>8.450233708062953e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>8.534751262043355e-06</v>
+        <v>8.534751262043296e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>9.576379086836172e-06</v>
+        <v>9.576379086836116e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>8.423455103458143e-06</v>
+        <v>8.423455103458136e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>9.144155177172736e-06</v>
+        <v>9.144155177172682e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.615046003436872e-06</v>
+        <v>5.615046003436763e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>9.697706258211208e-06</v>
+        <v>9.697706258211145e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.56259441916722e-05</v>
+        <v>1.562594419167212e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.164076514382623e-05</v>
+        <v>1.164076514382617e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.787144762495903e-06</v>
+        <v>8.787144762495837e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.622325410475347e-06</v>
+        <v>9.622325410475288e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.957288833126274e-06</v>
+        <v>8.957288833126281e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.595910932432479e-06</v>
+        <v>8.595910932432191e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>8.849261174350973e-06</v>
+        <v>8.84926117434848e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.692533044671944e-06</v>
+        <v>8.692533044671939e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>8.627418921091812e-06</v>
+        <v>8.627418921091807e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>8.881156331014359e-06</v>
+        <v>8.881156331014281e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>8.335396327737768e-06</v>
+        <v>8.335396327737753e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="M5" t="n">
         <v>8.827249050065126e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>8.649029040797729e-06</v>
+        <v>8.649029040797722e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>8.699356964077044e-06</v>
+        <v>8.699356964077034e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>8.687020373987892e-06</v>
+        <v>8.687020373987865e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.549481207192348e-06</v>
+        <v>8.549481207192309e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>8.717012791067132e-06</v>
+        <v>8.717012791067133e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>5.477034230871243e-06</v>
+        <v>5.477034230871142e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>8.832213510900154e-06</v>
+        <v>8.832213510900116e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>8.571134552548666e-06</v>
+        <v>8.571134552548546e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.067343506269805e-06</v>
+        <v>9.067343506269697e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.591522353201395e-06</v>
+        <v>8.591522353201383e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.832167079793139e-06</v>
+        <v>8.832167079793031e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.075752557600387e-06</v>
+        <v>9.075752557600379e-06</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.306375527798795e-07</v>
+        <v>6.306375527798277e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>5.930427200728253e-07</v>
+        <v>5.930427200721362e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>5.350798932775702e-07</v>
+        <v>5.350798932775154e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>6.178070115776238e-07</v>
+        <v>6.178070115776212e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.931077558396993e-07</v>
+        <v>6.931077558396973e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.127198768465526e-06</v>
+        <v>1.127198768465436e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>5.630421640045776e-07</v>
+        <v>5.630421640045194e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.01841517296256e-06</v>
+        <v>1.018415172962504e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.110401984997882e-06</v>
+        <v>1.110401984997818e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.706114182714058e-06</v>
+        <v>1.706114182714003e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.066641036720556e-06</v>
+        <v>1.066641036720506e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.174098872302016e-06</v>
+        <v>1.17409887230201e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>5.306139529644184e-07</v>
+        <v>5.306139529643737e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>6.288809836368263e-07</v>
+        <v>6.288809836367713e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.482468369445824e-07</v>
+        <v>4.482468369445234e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.55132645775365e-07</v>
+        <v>5.551326457754702e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>6.39650199755873e-07</v>
+        <v>6.396501997558206e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.681278024548694e-06</v>
+        <v>1.681278024548637e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>5.283540411706574e-07</v>
+        <v>5.283540411706562e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.225967555060888e-06</v>
+        <v>1.225967555060834e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>9.770634924400222e-07</v>
+        <v>9.770634924400174e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.779518636099358e-06</v>
+        <v>1.779518636099297e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>7.707756569560355e-06</v>
+        <v>7.707756569560272e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.745664081538744e-06</v>
+        <v>3.745664081538689e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.920437002084306e-07</v>
+        <v>8.920437002083739e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.727224348187872e-06</v>
+        <v>1.727224348187817e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.0621877708388e-06</v>
+        <v>1.062187770838797e-06</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.008098701449893e-07</v>
+        <v>7.008098701447246e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.541601120634945e-07</v>
+        <v>9.541601120616795e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>7.974319823844688e-07</v>
+        <v>7.974319823844634e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>7.323178588043339e-07</v>
+        <v>7.323178588043291e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.629687089025218e-07</v>
+        <v>9.629687089024189e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.100064784039033e-07</v>
+        <v>9.100064784037907e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.32147987777643e-07</v>
+        <v>9.321479877776371e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>7.539279785102672e-07</v>
+        <v>7.539279785102462e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>7.81169341965199e-07</v>
+        <v>7.811693419651821e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>7.688327518760443e-07</v>
+        <v>7.688327518760146e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.543801449048496e-07</v>
+        <v>6.543801449048316e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>7.988251689552779e-07</v>
+        <v>7.988251689552782e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>8.390517198744427e-07</v>
+        <v>8.390517198743981e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>9.140258887883124e-07</v>
+        <v>9.140258887882626e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>6.529469304367894e-07</v>
+        <v>6.529469304366814e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.172242443982334e-06</v>
+        <v>1.172242443982228e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.964212909139356e-07</v>
+        <v>6.964212909138988e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.370660175056628e-07</v>
+        <v>9.370660175055656e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.1806514953129e-06</v>
+        <v>1.180651495312893e-06</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344970632455057e-06</v>
+        <v>1.34497063245503e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.041865964908804e-06</v>
+        <v>1.041865964908807e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.17941604171065e-06</v>
+        <v>2.1794160417106e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.620176684751496e-07</v>
+        <v>7.62017668475151e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.277486900486415e-06</v>
+        <v>1.27748690048641e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.412081502564437e-06</v>
+        <v>1.412081502564397e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>9.319054381614142e-07</v>
+        <v>9.319054381614587e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.562203532014001e-06</v>
+        <v>2.562203532013967e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.104671342999752e-06</v>
+        <v>2.104671342999811e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.809614850562849e-06</v>
+        <v>5.809614850562811e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.759654213003275e-06</v>
+        <v>1.759654213003245e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.578958790668227e-06</v>
+        <v>2.578958790668236e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>8.161779748465447e-07</v>
+        <v>8.161779748465087e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.195293598692271e-06</v>
+        <v>1.195293598692225e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>7.445003288810439e-07</v>
+        <v>7.445003288810494e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.160837765524388e-06</v>
+        <v>1.160837765524348e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.300050252732073e-06</v>
+        <v>1.300050252732047e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>3.136807419662386e-06</v>
+        <v>3.13680741966229e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.177858708835358e-06</v>
+        <v>1.177858708835314e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>3.289104105898711e-06</v>
+        <v>3.289104105898663e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>2.931448637459058e-06</v>
+        <v>2.931448637459059e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.692430992052482e-06</v>
+        <v>1.69243099205245e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>2.218109018932015e-05</v>
+        <v>2.218109018932012e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.090521697422038e-06</v>
+        <v>7.090521697422006e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.338203706026036e-06</v>
+        <v>1.338203706025961e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.370742713772782e-06</v>
+        <v>2.37074271377277e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.012767068308844e-06</v>
+        <v>5.01276706830883e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.31502542690244e-06</v>
+        <v>1.315025426902445e-06</v>
       </c>
       <c r="C3" t="n">
         <v>1.978922175673314e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.604645257688047e-06</v>
+        <v>1.604645257688046e-06</v>
       </c>
       <c r="F3" t="n">
         <v>1.411996344708916e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.09433488341716e-06</v>
+        <v>2.094334883417126e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.956608829559097e-06</v>
+        <v>1.956608829559124e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>1.957248713619402e-06</v>
+        <v>1.957248713619406e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.460147642252538e-06</v>
+        <v>1.460147642252473e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.597646885824026e-06</v>
+        <v>1.597646885823866e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.563942498776785e-06</v>
+        <v>1.563942498776749e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.188176320405877e-06</v>
+        <v>1.188176320405816e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64595496605861e-06</v>
+        <v>1.645954966058604e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.774867907687297e-06</v>
+        <v>1.774867907687294e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.960619834075691e-06</v>
+        <v>1.960619834075548e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.24733470432271e-06</v>
+        <v>1.24733470432272e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.603132439675109e-06</v>
+        <v>2.603132439675021e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.303035535699147e-06</v>
+        <v>1.303035535699146e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.960492981202823e-06</v>
+        <v>1.96049298120277e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.642615561344315e-06</v>
+        <v>2.642615561344318e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.543802530301218e-06</v>
+        <v>8.543802530301184e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>8.445036407707854e-06</v>
+        <v>8.445036407707852e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>8.847948083422178e-06</v>
+        <v>8.847948083422129e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.323598190175343e-06</v>
+        <v>8.323598190175348e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>8.516926949169783e-06</v>
+        <v>8.516926949169778e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>8.568263654400475e-06</v>
+        <v>8.568263654400416e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.393245117437611e-06</v>
+        <v>8.393245117437573e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>8.987469628720104e-06</v>
+        <v>8.987469628720065e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.343312958945249e-06</v>
+        <v>8.343312958945207e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.017111292130222e-05</v>
+        <v>1.017111292130211e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.694949825950605e-06</v>
+        <v>8.694949825950552e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>8.991514953603963e-06</v>
+        <v>8.991514953603966e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>8.351063815999795e-06</v>
+        <v>8.351063815999751e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>8.489247009091151e-06</v>
+        <v>8.489247009091101e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>8.324938155726822e-06</v>
+        <v>8.324938155726761e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.476688262502278e-06</v>
+        <v>8.476688262502226e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>8.527429579373916e-06</v>
+        <v>8.527429579373872e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>9.19690599842841e-06</v>
+        <v>9.196905998428339e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>8.482892196469112e-06</v>
+        <v>8.48289219646907e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>9.252416352203584e-06</v>
+        <v>9.252416352203513e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>5.947281594303752e-06</v>
+        <v>5.947281594303813e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>8.670447751288948e-06</v>
+        <v>8.670447751288898e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.613832343870989e-05</v>
+        <v>1.613832343870979e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.063798842581479e-05</v>
+        <v>1.063798842581472e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.541336065079111e-06</v>
+        <v>8.541336065079041e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.917684408717626e-06</v>
+        <v>8.917684408717555e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.885677662170937e-06</v>
+        <v>9.885677662170908e-06</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.532887854511674e-06</v>
+        <v>8.532887854511645e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>8.786582393061942e-06</v>
+        <v>8.786582393061937e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.630726051810743e-06</v>
+        <v>8.63072605181073e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>8.565954062099253e-06</v>
+        <v>8.565954062099246e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>8.816937000297562e-06</v>
+        <v>8.816937000297593e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>8.289345911433942e-06</v>
+        <v>8.289345911433899e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>8.764908931007973e-06</v>
+        <v>8.764908931007983e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>8.585783197895591e-06</v>
+        <v>8.585783197895576e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>8.635900057579729e-06</v>
+        <v>8.635900057579755e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>8.623615204278097e-06</v>
+        <v>8.623615204277971e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.486652844731052e-06</v>
+        <v>8.486652844731001e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>8.653507785563229e-06</v>
+        <v>8.653507785563162e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>5.525721499558552e-06</v>
+        <v>5.525721499558616e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>8.768199434973982e-06</v>
+        <v>8.768199434973949e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>8.508215380995976e-06</v>
+        <v>8.508215380995884e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.002387734951086e-06</v>
+        <v>9.002387734951013e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.528517679960477e-06</v>
+        <v>8.528517679960448e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.768153198591415e-06</v>
+        <v>8.768153198591404e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.021785269606518e-06</v>
+        <v>9.021785269606504e-06</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.035613903142535e-07</v>
+        <v>7.035613903141063e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>6.047952677207796e-07</v>
+        <v>6.047952677207761e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.007706943435196e-06</v>
+        <v>1.007706943435063e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.833570501882803e-07</v>
+        <v>4.833570501882801e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.766858091827089e-07</v>
+        <v>6.766858091827091e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>7.048084091974111e-07</v>
+        <v>7.048084091973901e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>5.530039774506209e-07</v>
+        <v>5.530039774505003e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.14722848873314e-06</v>
+        <v>1.147228488732987e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>9.563996010421661e-07</v>
+        <v>9.563996010421291e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>2.33087178131523e-06</v>
+        <v>2.330871781315048e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>8.547086859636312e-07</v>
+        <v>8.547086859634804e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15127381361689e-06</v>
+        <v>1.151273813616894e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>5.108226760128315e-07</v>
+        <v>5.108226760126853e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>6.257917638881102e-07</v>
+        <v>6.25791763888065e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>4.614829105237921e-07</v>
+        <v>4.614829105237203e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.364471225152925e-07</v>
+        <v>6.364471225151637e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>6.871884393869503e-07</v>
+        <v>6.871884393868115e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.356664858441441e-06</v>
+        <v>1.356664858441277e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.426510564821292e-07</v>
+        <v>6.426510564820007e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.388961107000539e-06</v>
+        <v>1.388961107000476e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.255552677018772e-06</v>
+        <v>1.255552677018769e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>8.069925060859135e-07</v>
+        <v>8.069925060858656e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>8.274868193506869e-06</v>
+        <v>8.274868193506761e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.797747285827813e-06</v>
+        <v>2.797747285827648e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.010949250920676e-07</v>
+        <v>7.010949250919761e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.077443268730642e-06</v>
+        <v>1.077443268730486e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.045436522183863e-06</v>
+        <v>2.045436522183844e-06</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.92646714524592e-07</v>
+        <v>6.926467145245758e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>9.463412530748758e-07</v>
+        <v>9.463412530748718e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>7.904849118236715e-07</v>
+        <v>7.904849118236705e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>7.257129221121716e-07</v>
+        <v>7.257129221121714e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>9.534817550945417e-07</v>
+        <v>9.534817550945652e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>9.024325535308447e-07</v>
+        <v>9.02432553530821e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>9.246677910209015e-07</v>
+        <v>9.246677910209107e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>7.455420579086375e-07</v>
+        <v>7.455420579085085e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>7.72444812376724e-07</v>
+        <v>7.724448123767339e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>7.601599590750548e-07</v>
+        <v>7.601599590749517e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.464117047439749e-07</v>
+        <v>6.464117047439374e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="T7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>7.900525403601946e-07</v>
+        <v>7.900525403601383e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>8.339925822735837e-07</v>
+        <v>8.339925822735818e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>9.047441897709205e-07</v>
+        <v>9.047441897709133e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>6.447601357929314e-07</v>
+        <v>6.447601357928357e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.162146594964083e-06</v>
+        <v>1.16214659496395e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.882765399733442e-07</v>
+        <v>6.882765399733653e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.279120586043531e-07</v>
+        <v>9.279120586043323e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.181544129619447e-06</v>
+        <v>1.181544129619433e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.320497170815766e-05</v>
+        <v>6.320497170815808e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.78287215690493e-06</v>
+        <v>1.782872156905138e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>9.142284814438781e-06</v>
+        <v>9.142284814439297e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.23695965516166e-05</v>
+        <v>2.236959655161726e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>5.879541156926002e-06</v>
+        <v>5.879541156925998e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.936148903192059e-05</v>
+        <v>1.936148903192113e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.897074821155939e-06</v>
+        <v>2.897074821156425e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.744126935287e-06</v>
+        <v>4.744126935287434e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.955905216117716e-05</v>
+        <v>2.955905216117733e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.806034874149685e-06</v>
+        <v>3.806034874150154e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001820853614352086</v>
+        <v>0.0001820853614352091</v>
       </c>
       <c r="M2" t="n">
-        <v>6.855817803453743e-05</v>
+        <v>6.855817803453746e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.732579779875801e-06</v>
+        <v>2.732579779876251e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>7.457843261543658e-06</v>
+        <v>7.457843261544053e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>4.31460925496155e-05</v>
+        <v>4.314609254961574e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.068053796569207e-05</v>
+        <v>1.068053796569254e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.100627139124474e-06</v>
+        <v>4.100627139124241e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>3.278061339345454e-05</v>
+        <v>3.278061339345499e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>9.412796499905244e-06</v>
+        <v>9.412796499905735e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001113342501893</v>
+        <v>0.0001113342501893007</v>
       </c>
       <c r="V2" t="n">
-        <v>1.377754109560408e-05</v>
+        <v>1.37775410956041e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.879452188380256e-05</v>
+        <v>1.879452188380314e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>6.929140335112772e-05</v>
+        <v>6.929140335112839e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.953238946556289e-05</v>
+        <v>1.953238946556333e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.564198397052067e-05</v>
+        <v>3.564198397052107e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.157783208197611e-05</v>
+        <v>3.157783208197657e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.934596021035739e-05</v>
+        <v>7.934596021035737e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.962649198844927e-06</v>
+        <v>1.962649198845597e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.692900628005963e-06</v>
+        <v>2.69290062800593e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>2.254755260145595e-06</v>
+        <v>2.254755260146225e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.98882130672863e-06</v>
+        <v>1.988821306728631e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.941281113222708e-06</v>
+        <v>2.941281113222844e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.732053844006469e-06</v>
+        <v>2.732053844006545e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.844946977003524e-06</v>
+        <v>2.844946977003528e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.144889039821027e-06</v>
+        <v>2.144889039821372e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>2.317556196412584e-06</v>
+        <v>2.317556196412833e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.27523130410879e-06</v>
+        <v>2.275231304109296e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.803356144089896e-06</v>
+        <v>1.803356144089986e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>2.377457574368879e-06</v>
+        <v>2.377457574368905e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>2.441854497757361e-06</v>
+        <v>2.44185449775744e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>2.773366026827182e-06</v>
+        <v>2.773366026827839e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.877645352336749e-06</v>
+        <v>1.877645352337336e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.578908641089666e-06</v>
+        <v>3.578908641089894e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.94759267658226e-06</v>
+        <v>1.947592676582319e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.773206729044014e-06</v>
+        <v>2.773206729044466e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.774716836652191e-06</v>
+        <v>3.774716836652197e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.320539176344192e-05</v>
+        <v>3.320539176344264e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.076672226150625e-05</v>
+        <v>1.076672226150662e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.350017722680232e-05</v>
+        <v>1.350017722680319e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.826618061673278e-05</v>
+        <v>1.826618061673339e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.224732866543918e-05</v>
+        <v>1.224732866543935e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.722495716412006e-05</v>
+        <v>1.722495716412069e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.122387151920902e-05</v>
+        <v>1.122387151920971e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.189710032562884e-05</v>
+        <v>1.189710032562968e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.031335565016717e-05</v>
+        <v>2.031335565016729e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.155517678497743e-05</v>
+        <v>1.15551767849781e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.653589785493654e-05</v>
+        <v>7.653589785493722e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.520216437887963e-05</v>
+        <v>3.520216437887997e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.116391500826075e-05</v>
+        <v>1.116391500826143e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.288621806048345e-05</v>
+        <v>1.288621806048408e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.589416585340444e-05</v>
+        <v>2.589416585340502e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.406085243735376e-05</v>
+        <v>1.406085243735444e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.166255220628372e-05</v>
+        <v>1.16625522062844e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.211607041858527e-05</v>
+        <v>2.211607041858593e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.359877555964631e-05</v>
+        <v>1.359877555964701e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>5.074794860729651e-05</v>
+        <v>5.074794860729721e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.110131227873508e-05</v>
+        <v>1.110131227873504e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.701830429629538e-05</v>
+        <v>1.701830429629636e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>3.542382462681578e-05</v>
+        <v>3.542382462681654e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.728724836536841e-05</v>
+        <v>1.728724836536923e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.315900639401611e-05</v>
+        <v>2.315900639401693e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.167767075432261e-05</v>
+        <v>2.167767075432339e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.91869792792557e-05</v>
+        <v>3.918697927925591e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.088328435245628e-05</v>
+        <v>1.088328435245723e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.10984169531288e-05</v>
+        <v>1.109841695312902e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.093455716638325e-05</v>
+        <v>1.093455716638408e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.082920696718134e-05</v>
+        <v>1.082920696718148e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.123998419357089e-05</v>
+        <v>1.123998419357154e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.053522978207727e-05</v>
+        <v>1.053522978207792e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.125046330212625e-05</v>
+        <v>1.125046330212639e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.094970863452387e-05</v>
+        <v>1.094970863452435e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.101264378554138e-05</v>
+        <v>1.101264378554153e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.099721685930061e-05</v>
+        <v>1.0997216859301e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.082522390451158e-05</v>
+        <v>1.082522390451228e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.103447713440896e-05</v>
+        <v>1.103447713440971e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>6.969587624172475e-06</v>
+        <v>6.969587624172542e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.117878111633821e-05</v>
+        <v>1.117878111633888e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.085230144856969e-05</v>
+        <v>1.085230144857062e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.147239194007797e-05</v>
+        <v>1.147239194007811e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.08777964268942e-05</v>
+        <v>1.087779642689506e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.117872305416683e-05</v>
+        <v>1.117872305416745e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.164214847188285e-05</v>
+        <v>1.164214847188312e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.350079219753905e-05</v>
+        <v>2.350079219753959e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.062122695603516e-06</v>
+        <v>1.062122695603531e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>3.795577660899538e-06</v>
+        <v>3.795577660900127e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>8.561581050829918e-06</v>
+        <v>8.561581050830426e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>2.542729099536373e-06</v>
+        <v>2.542729099536371e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.493607178668281e-06</v>
+        <v>7.493607178668794e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.519271953306246e-06</v>
+        <v>1.51927195330675e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.192500759726052e-06</v>
+        <v>2.192500759726571e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.118610112901333e-05</v>
+        <v>1.118610112901366e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.85057721907464e-06</v>
+        <v>1.85057721907509e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.683129828903391e-05</v>
+        <v>6.683129828903433e-05</v>
       </c>
       <c r="M6" t="n">
         <v>2.549756481297685e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.459315442357935e-06</v>
+        <v>1.459315442358434e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>3.154868075031674e-06</v>
+        <v>3.154868075032176e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.616281586795266e-05</v>
+        <v>1.616281586795294e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.356252871450926e-06</v>
+        <v>4.356252871451455e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.957952640380925e-06</v>
+        <v>1.957952640381479e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.241147085268248e-05</v>
+        <v>1.241147085268296e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.89417599374352e-06</v>
+        <v>3.894175993744028e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>4.101659862184472e-05</v>
+        <v>4.101659862184519e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>5.391989074987777e-06</v>
+        <v>5.391989074987741e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>7.286954310843631e-06</v>
+        <v>7.286954310844368e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.569247464136397e-05</v>
+        <v>2.569247464136457e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.582648799465644e-06</v>
+        <v>7.582648799466147e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.345440682811334e-05</v>
+        <v>1.345440682811384e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.19730711884198e-05</v>
+        <v>1.197307118842033e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.948237971335287e-05</v>
+        <v>2.948237971335289e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.178684786553497e-06</v>
+        <v>1.178684786554125e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.39381738722597e-06</v>
+        <v>1.393817387225945e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.229957600480463e-06</v>
+        <v>1.229957600480922e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.124607401278556e-06</v>
+        <v>1.124607401278557e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.508634208119107e-06</v>
+        <v>1.508634208119605e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.407975260923446e-06</v>
+        <v>1.407975260923683e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.545863736223453e-06</v>
+        <v>1.545863736223455e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.245109068621073e-06</v>
+        <v>1.245109068621368e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>1.281293800089573e-06</v>
+        <v>1.281293800089641e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.265866873848813e-06</v>
+        <v>1.265866873849004e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.120624338608798e-06</v>
+        <v>1.120624338609228e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.303127148957161e-06</v>
+        <v>1.303127148957624e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.260264420425188e-06</v>
+        <v>1.260264420425128e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.447431130886447e-06</v>
+        <v>1.447431130887001e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.120951463117874e-06</v>
+        <v>1.120951463118543e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.767792374175146e-06</v>
+        <v>1.767792374175162e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.173196860991376e-06</v>
+        <v>1.173196860991962e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.47412348826402e-06</v>
+        <v>1.474123488264503e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.937548905980061e-06</v>
+        <v>1.937548905980067e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.139202890632411e-06</v>
+        <v>1.139202890632419e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.004968135830219e-06</v>
+        <v>1.00496813583022e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.755623721417865e-06</v>
+        <v>3.755623721417876e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.071605012502676e-06</v>
+        <v>2.071605012502679e-06</v>
       </c>
       <c r="F2" t="n">
         <v>1.097474422340251e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.416741442242147e-05</v>
+        <v>1.416741442242148e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>9.555850306619881e-07</v>
+        <v>9.555850306619934e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.332416451624367e-06</v>
+        <v>3.332416451624376e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.009741926017223e-05</v>
+        <v>1.009741926017211e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.114469973583632e-05</v>
+        <v>1.114469973583633e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>5.615139060205549e-05</v>
+        <v>5.615139060205543e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.084197418740185e-05</v>
+        <v>1.084197418740184e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>9.502488929953831e-07</v>
+        <v>9.502488929953907e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.898739084406277e-06</v>
+        <v>1.898739084406284e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.824358329302187e-05</v>
+        <v>1.824358329302188e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.172125849407299e-06</v>
+        <v>1.172125849407309e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.258852903618649e-06</v>
+        <v>1.258852903618657e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>8.416044408208056e-06</v>
+        <v>8.416044408208065e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.082239966432313e-06</v>
+        <v>1.082239966432315e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.743412794368513e-05</v>
+        <v>1.743412794368516e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.525386962913845e-06</v>
+        <v>2.525386962913846e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.25243171635168e-06</v>
+        <v>6.252431716351691e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>4.357613411000338e-05</v>
+        <v>4.357613411000339e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.218936644868798e-05</v>
+        <v>3.218936644868796e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.845060068140532e-06</v>
+        <v>4.845060068140545e-06</v>
       </c>
       <c r="AA2" t="n">
         <v>1.175955846738694e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.040001595657447e-05</v>
+        <v>5.04000159565745e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.521006176391427e-06</v>
+        <v>1.521006176391435e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.226891383445482e-06</v>
+        <v>2.226891383445486e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.818759402059528e-06</v>
+        <v>1.818759402059529e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.606751011959411e-06</v>
+        <v>1.606751011959413e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.368935468352069e-06</v>
+        <v>2.368935468352081e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.210641044639923e-06</v>
+        <v>2.210641044639928e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.225143721690847e-06</v>
+        <v>2.225143721690851e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.678906707793437e-06</v>
+        <v>1.678906707793446e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.828513048731843e-06</v>
+        <v>1.82851304873185e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>1.791840919571663e-06</v>
+        <v>1.791840919571677e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.382987739480451e-06</v>
+        <v>1.382987739480462e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.880622867925601e-06</v>
+        <v>1.880622867925608e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.998497442893357e-06</v>
+        <v>1.998497442893359e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>2.223446527903256e-06</v>
+        <v>2.223446527903269e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.447355143431144e-06</v>
+        <v>1.44735514343115e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.921760668074925e-06</v>
+        <v>2.921760668074934e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.507960550069415e-06</v>
+        <v>1.507960550069425e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.22330850536449e-06</v>
+        <v>2.2233085053645e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.104091092294965e-06</v>
+        <v>3.104091092294969e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6918,34 +6918,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.236976377688865e-06</v>
+        <v>9.23697637768888e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>9.190326346920292e-06</v>
+        <v>9.190326346920296e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.01906310469456e-05</v>
+        <v>1.019063104694562e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.557383264235617e-06</v>
+        <v>9.557383264235622e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.206727036610688e-06</v>
+        <v>9.206727036610702e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.398560649604229e-05</v>
+        <v>1.39856064960423e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>9.170049823879408e-06</v>
+        <v>9.170049823879423e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.003637696665654e-05</v>
+        <v>1.003637696665656e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.192185194754463e-05</v>
+        <v>1.192185194754464e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.288386248728989e-05</v>
+        <v>1.288386248728991e-05</v>
       </c>
       <c r="L4" t="n">
         <v>2.928827281278006e-05</v>
@@ -6954,46 +6954,46 @@
         <v>1.277468888119404e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>9.16810486436004e-06</v>
+        <v>9.168104864360059e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.513818401395156e-06</v>
+        <v>9.513818401395174e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.547132218458467e-05</v>
+        <v>1.547132218458468e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.248976409561414e-06</v>
+        <v>9.248976409561428e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>9.280587402420962e-06</v>
+        <v>9.280587402420984e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.188929966185794e-05</v>
+        <v>1.188929966185796e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>9.216214060710351e-06</v>
+        <v>9.216214060710378e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.517628521485602e-05</v>
+        <v>1.517628521485605e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.903439562767016e-06</v>
+        <v>5.90343956276681e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.110068824209925e-05</v>
+        <v>1.110068824209926e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>2.470473948754412e-05</v>
+        <v>2.470473948754415e-05</v>
       </c>
       <c r="Y4" t="n">
         <v>2.055439638517126e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.058771780251854e-05</v>
+        <v>1.058771780251856e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.310797127490434e-05</v>
+        <v>1.310797127490436e-05</v>
       </c>
       <c r="AB4" t="n">
         <v>2.728549196824379e-05</v>
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.376139191987497e-06</v>
+        <v>9.376139191987507e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>9.635703022128851e-06</v>
+        <v>9.635703022128868e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>9.465224008292152e-06</v>
+        <v>9.465224008292167e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>9.392352373299214e-06</v>
+        <v>9.392352373299235e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>9.685199462018706e-06</v>
+        <v>9.685199462018713e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>9.047213899208714e-06</v>
+        <v>9.047213899208726e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>9.633955360374267e-06</v>
+        <v>9.63395536037428e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>9.43369208152187e-06</v>
+        <v>9.433692081521887e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>9.488221836027574e-06</v>
+        <v>9.488221836027583e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>9.474855275574573e-06</v>
+        <v>9.4748552755746e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.325833092427761e-06</v>
+        <v>9.325833092427786e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>9.507215253219309e-06</v>
+        <v>9.507215253219331e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>5.711394519768672e-06</v>
+        <v>5.711394519768447e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>9.632170451642488e-06</v>
+        <v>9.632170451642508e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>9.349294255327562e-06</v>
+        <v>9.349294255327581e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.886697755716436e-06</v>
+        <v>9.886697755716454e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.371384214382585e-06</v>
+        <v>9.371384214382607e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.632120144047867e-06</v>
+        <v>9.632120144047877e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.004668273200344e-05</v>
+        <v>1.004668273200347e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.038136942154815e-07</v>
+        <v>7.038136942154906e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>6.571636634469101e-07</v>
+        <v>6.571636634469094e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.65746836347222e-06</v>
+        <v>1.657468363472228e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.024220580762235e-06</v>
+        <v>1.024220580762236e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.735643531373039e-07</v>
+        <v>6.735643531373036e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>5.428034858482687e-06</v>
+        <v>5.428034858482692e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.368871404060355e-07</v>
+        <v>6.368871404060394e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.503214283183154e-06</v>
+        <v>1.503214283183161e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.938177591164964e-06</v>
+        <v>3.938177591164994e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.35069980381651e-06</v>
+        <v>4.350699803816523e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>2.075511012930664e-05</v>
+        <v>2.075511012930665e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.241526197720637e-06</v>
+        <v>4.24152619772064e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>6.349421808866533e-07</v>
+        <v>6.349421808866627e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>9.56246763835555e-07</v>
+        <v>9.562467638355654e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>6.913750547025063e-06</v>
+        <v>6.913750547025078e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.158137260880311e-07</v>
+        <v>7.158137260880381e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.4742471894758e-07</v>
+        <v>7.474247189475871e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35613697838457e-06</v>
+        <v>3.356136978384577e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>6.830513772369692e-07</v>
+        <v>6.830513772369818e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>6.618713577296417e-06</v>
+        <v>6.618713577296441e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.16691302770605e-06</v>
+        <v>1.166913027706051e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>2.543116604539648e-06</v>
+        <v>2.543116604539659e-06</v>
       </c>
       <c r="X6" t="n">
         <v>1.614716784998454e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.20212337016979e-05</v>
+        <v>1.202123370169789e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.054555119045169e-06</v>
+        <v>2.054555119045175e-06</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.574808591430964e-06</v>
+        <v>4.57480859143097e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.875232928477043e-05</v>
+        <v>1.875232928477042e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.429765085141127e-07</v>
+        <v>8.429765085141157e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.102540338655472e-06</v>
+        <v>1.102540338655474e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>9.320613248187666e-07</v>
+        <v>9.320613248187671e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>8.591896898258442e-07</v>
+        <v>8.591896898258449e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.127627824459101e-06</v>
+        <v>1.127627824459109e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.063539542829057e-06</v>
+        <v>1.063539542829063e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.100792676900875e-06</v>
+        <v>1.100792676900876e-06</v>
       </c>
       <c r="N7" t="n">
         <v>9.005293980484965e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>9.306501984679722e-07</v>
+        <v>9.306501984679783e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>9.172836380149712e-07</v>
+        <v>9.172836380149777e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.926704089543727e-07</v>
+        <v>7.926704089543774e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>9.496436156597082e-07</v>
+        <v>9.496436156597131e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>9.748679847076965e-07</v>
+        <v>9.748679847076978e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.074598814082903e-06</v>
+        <v>1.074598814082911e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>7.917226177679601e-07</v>
+        <v>7.917226177679705e-07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.353535072243061e-06</v>
+        <v>1.353535072243062e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.382215309092139e-07</v>
+        <v>8.382215309092217e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.098957460574483e-06</v>
+        <v>1.098957460574485e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.513520048530071e-06</v>
+        <v>1.513520048530072e-06</v>
       </c>
     </row>
   </sheetData>
